--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_ADJR2.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,68 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -358,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -390,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -425,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -601,2379 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>-3.1935954698844048E-2</v>
+        <v>-0.0309091624346408</v>
       </c>
       <c r="C2">
-        <v>-4.9017002109169067E-2</v>
+        <v>-0.05257945569618049</v>
       </c>
       <c r="D2">
-        <v>-5.5380338461749022E-2</v>
+        <v>-0.05908733374849533</v>
       </c>
       <c r="E2">
-        <v>-5.7714960240683753E-2</v>
+        <v>-0.06221966240973618</v>
       </c>
       <c r="F2">
-        <v>-5.709540823700094E-2</v>
+        <v>-0.05621151993175835</v>
       </c>
       <c r="G2">
-        <v>-7.0489705428451552E-2</v>
+        <v>-0.06652286286126899</v>
       </c>
       <c r="H2">
-        <v>1.213399169249618E-3</v>
+        <v>-0.005236771100586484</v>
       </c>
       <c r="I2">
-        <v>8.734244263056079E-2</v>
+        <v>0.08428563584582191</v>
       </c>
       <c r="J2">
-        <v>4.2477297006538392E-2</v>
+        <v>0.04694856235413453</v>
       </c>
       <c r="K2">
-        <v>8.6540913788585333E-2</v>
+        <v>0.0822075714738514</v>
       </c>
       <c r="L2">
-        <v>0.1878233278671716</v>
+        <v>0.1798434835851796</v>
       </c>
       <c r="M2">
-        <v>0.22233231212555321</v>
+        <v>0.213295625583303</v>
       </c>
       <c r="N2">
-        <v>0.30719258702085761</v>
+        <v>0.3006234988040885</v>
       </c>
       <c r="O2">
-        <v>0.38328421254344303</v>
+        <v>0.3778582454072691</v>
       </c>
       <c r="P2">
-        <v>0.42279307213471751</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4239042078922813</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>-2.1798011290991098E-2</v>
+        <v>-0.02099456057005921</v>
       </c>
       <c r="C3">
-        <v>-5.3790172592578213E-2</v>
+        <v>-0.04628140601128741</v>
       </c>
       <c r="D3">
-        <v>-0.1767578638300685</v>
+        <v>-0.1715025286902799</v>
       </c>
       <c r="E3">
-        <v>1.268278224332082E-2</v>
+        <v>0.0222596911735379</v>
       </c>
       <c r="F3">
-        <v>0.10921434133345689</v>
+        <v>0.1215331771838012</v>
       </c>
       <c r="G3">
-        <v>0.17673942452486599</v>
+        <v>0.1742301648650524</v>
       </c>
       <c r="H3">
-        <v>0.22364580866523051</v>
+        <v>0.2175184304848574</v>
       </c>
       <c r="I3">
-        <v>0.24658073340486791</v>
+        <v>0.2344787249557625</v>
       </c>
       <c r="J3">
-        <v>0.31509393425092758</v>
+        <v>0.2981525886886429</v>
       </c>
       <c r="K3">
-        <v>0.35849369298210948</v>
+        <v>0.3414081779645546</v>
       </c>
       <c r="L3">
-        <v>0.3550480558825681</v>
+        <v>0.3403000110217872</v>
       </c>
       <c r="M3">
-        <v>0.36361839224681031</v>
+        <v>0.3452628011114079</v>
       </c>
       <c r="N3">
-        <v>0.33684091118400328</v>
+        <v>0.3191178717462257</v>
       </c>
       <c r="O3">
-        <v>0.32704178046761251</v>
+        <v>0.3196921508602512</v>
       </c>
       <c r="P3">
-        <v>0.34975454221098168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.3449017399220294</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>-3.2041195703372417E-2</v>
+        <v>-0.03391041880822396</v>
       </c>
       <c r="C4">
-        <v>-4.6907574734430052E-2</v>
+        <v>-0.04450085330911528</v>
       </c>
       <c r="D4">
-        <v>-0.13265339914183569</v>
+        <v>-0.1218205332258667</v>
       </c>
       <c r="E4">
-        <v>-0.12683083934189071</v>
+        <v>-0.1151296686492731</v>
       </c>
       <c r="F4">
-        <v>-0.19128686593106181</v>
+        <v>-0.1753046999165144</v>
       </c>
       <c r="G4">
-        <v>-4.8989169694974029E-2</v>
+        <v>-0.0407882078006774</v>
       </c>
       <c r="H4">
-        <v>9.0996536810734552E-2</v>
+        <v>0.09876404245641386</v>
       </c>
       <c r="I4">
-        <v>9.2869912717498157E-2</v>
+        <v>0.115756660081455</v>
       </c>
       <c r="J4">
-        <v>0.1227383924396416</v>
+        <v>0.138888833608373</v>
       </c>
       <c r="K4">
-        <v>0.1958397799289516</v>
+        <v>0.1982275277741247</v>
       </c>
       <c r="L4">
-        <v>0.27020738405730249</v>
+        <v>0.273705796310258</v>
       </c>
       <c r="M4">
-        <v>0.32953228033763943</v>
+        <v>0.3342140765688415</v>
       </c>
       <c r="N4">
-        <v>0.37243937757159762</v>
+        <v>0.3774335296200462</v>
       </c>
       <c r="O4">
-        <v>0.38268500828502727</v>
+        <v>0.3836894878116494</v>
       </c>
       <c r="P4">
-        <v>0.37262390681109542</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.3800945285883095</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>-2.1837111729137569E-2</v>
+        <v>-0.02258972649150686</v>
       </c>
       <c r="C5">
-        <v>-6.3021356667235517E-2</v>
+        <v>-0.07406892567203299</v>
       </c>
       <c r="D5">
-        <v>-7.7706316606389728E-2</v>
+        <v>-0.07546516132249291</v>
       </c>
       <c r="E5">
-        <v>-0.12904440447663779</v>
+        <v>-0.1287928969767078</v>
       </c>
       <c r="F5">
-        <v>8.7760046638101233E-2</v>
+        <v>0.0883167245715652</v>
       </c>
       <c r="G5">
-        <v>0.18794274758729951</v>
+        <v>0.1939927682533635</v>
       </c>
       <c r="H5">
-        <v>0.24051515063118861</v>
+        <v>0.2389730620112396</v>
       </c>
       <c r="I5">
-        <v>0.2962147787311088</v>
+        <v>0.30175240713644</v>
       </c>
       <c r="J5">
-        <v>0.36923796284627358</v>
+        <v>0.3679258907915758</v>
       </c>
       <c r="K5">
-        <v>0.400946834772414</v>
+        <v>0.3985223993618913</v>
       </c>
       <c r="L5">
-        <v>0.4415419430517602</v>
+        <v>0.4344029400185744</v>
       </c>
       <c r="M5">
-        <v>0.44237953738722591</v>
+        <v>0.432770679606483</v>
       </c>
       <c r="N5">
-        <v>0.42435342838783119</v>
+        <v>0.4103732998420652</v>
       </c>
       <c r="O5">
-        <v>0.40451654822999972</v>
+        <v>0.3900654837708717</v>
       </c>
       <c r="P5">
-        <v>0.38071559656390902</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.3687432758577957</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>-2.176296220081958E-2</v>
+        <v>-0.02470151514924269</v>
       </c>
       <c r="C6">
-        <v>-6.3857546598376322E-2</v>
+        <v>-0.07422163510650634</v>
       </c>
       <c r="D6">
-        <v>-7.1522140362219114E-2</v>
+        <v>-0.06632916095550452</v>
       </c>
       <c r="E6">
-        <v>-6.461570156535712E-2</v>
+        <v>-0.05622015346963644</v>
       </c>
       <c r="F6">
-        <v>0.1505444284255274</v>
+        <v>0.1604677238239528</v>
       </c>
       <c r="G6">
-        <v>0.28156596506078813</v>
+        <v>0.2928380113995377</v>
       </c>
       <c r="H6">
-        <v>0.31386100519698279</v>
+        <v>0.3378272338052366</v>
       </c>
       <c r="I6">
-        <v>0.39388752906659757</v>
+        <v>0.4062027103969788</v>
       </c>
       <c r="J6">
-        <v>0.44058824744930902</v>
+        <v>0.4475410389668669</v>
       </c>
       <c r="K6">
-        <v>0.4610175244146284</v>
+        <v>0.4711427612549062</v>
       </c>
       <c r="L6">
-        <v>0.476993198930875</v>
+        <v>0.4885384199565682</v>
       </c>
       <c r="M6">
-        <v>0.48478027545179803</v>
+        <v>0.492700514931418</v>
       </c>
       <c r="N6">
-        <v>0.47776746603461639</v>
+        <v>0.4865439492426533</v>
       </c>
       <c r="O6">
-        <v>0.48561829411988</v>
+        <v>0.4923924714048941</v>
       </c>
       <c r="P6">
-        <v>0.4675903294206824</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.4804443180964985</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>-3.021792032740632E-2</v>
+        <v>-0.03749815348691349</v>
       </c>
       <c r="C7">
-        <v>-4.5180642808662727E-2</v>
+        <v>-0.05314375114110289</v>
       </c>
       <c r="D7">
-        <v>-0.13453204164845059</v>
+        <v>-0.1431042207696032</v>
       </c>
       <c r="E7">
-        <v>-0.14046259650549289</v>
+        <v>-0.1514386261633123</v>
       </c>
       <c r="F7">
-        <v>-0.18618716815423811</v>
+        <v>-0.1983417758320659</v>
       </c>
       <c r="G7">
-        <v>-0.1713261772047999</v>
+        <v>-0.1858145751046568</v>
       </c>
       <c r="H7">
-        <v>-1.9944236433045409E-2</v>
+        <v>-0.02690196213905235</v>
       </c>
       <c r="I7">
-        <v>0.1012185700541335</v>
+        <v>0.09514373636594353</v>
       </c>
       <c r="J7">
-        <v>9.3843950723890429E-2</v>
+        <v>0.09517416303117668</v>
       </c>
       <c r="K7">
-        <v>0.14165001755955359</v>
+        <v>0.1348576175260295</v>
       </c>
       <c r="L7">
-        <v>0.23293557593033409</v>
+        <v>0.2213037919388069</v>
       </c>
       <c r="M7">
-        <v>0.30086208787783558</v>
+        <v>0.2941299475923215</v>
       </c>
       <c r="N7">
-        <v>0.35049348987330048</v>
+        <v>0.3466617927572416</v>
       </c>
       <c r="O7">
-        <v>0.38118829149075251</v>
+        <v>0.3788309949068405</v>
       </c>
       <c r="P7">
-        <v>0.39232325562249448</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.3940881191588784</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>-2.7324609821182289E-2</v>
+        <v>-0.02822205152125482</v>
       </c>
       <c r="C8">
-        <v>-4.3366203684903099E-2</v>
+        <v>-0.04192576910322471</v>
       </c>
       <c r="D8">
-        <v>-0.12755068791128979</v>
+        <v>-0.1174881784458682</v>
       </c>
       <c r="E8">
-        <v>-0.1520644792200706</v>
+        <v>-0.1515404145752722</v>
       </c>
       <c r="F8">
-        <v>-9.4343674485205059E-2</v>
+        <v>-0.08011892868121069</v>
       </c>
       <c r="G8">
-        <v>1.156898772945459E-2</v>
+        <v>0.0145942061382597</v>
       </c>
       <c r="H8">
-        <v>6.6563596516941589E-2</v>
+        <v>0.07490112348261307</v>
       </c>
       <c r="I8">
-        <v>0.1644630133859952</v>
+        <v>0.1678207901555316</v>
       </c>
       <c r="J8">
-        <v>0.21183084261431631</v>
+        <v>0.2145275439454228</v>
       </c>
       <c r="K8">
-        <v>0.32659901490314358</v>
+        <v>0.3291252189387641</v>
       </c>
       <c r="L8">
-        <v>0.33075017809767282</v>
+        <v>0.3430413637435711</v>
       </c>
       <c r="M8">
-        <v>0.37874891590571719</v>
+        <v>0.3871785968134269</v>
       </c>
       <c r="N8">
-        <v>0.41714362178412667</v>
+        <v>0.4252945403284348</v>
       </c>
       <c r="O8">
-        <v>0.41770979734249952</v>
+        <v>0.4288182271323899</v>
       </c>
       <c r="P8">
-        <v>0.41612107139517829</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4192264052849704</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>-2.622862884281579E-2</v>
+        <v>-0.02500673426692134</v>
       </c>
       <c r="C9">
-        <v>-4.1785405151613733E-2</v>
+        <v>-0.03831791356756908</v>
       </c>
       <c r="D9">
-        <v>-0.11014036297698861</v>
+        <v>-0.1115692124485748</v>
       </c>
       <c r="E9">
-        <v>-0.13216296547433379</v>
+        <v>-0.1296625334604877</v>
       </c>
       <c r="F9">
-        <v>-7.6818741153683229E-2</v>
+        <v>-0.0778477268618899</v>
       </c>
       <c r="G9">
-        <v>1.877212916579311E-2</v>
+        <v>0.02009080281697788</v>
       </c>
       <c r="H9">
-        <v>6.4783595679735309E-2</v>
+        <v>0.07836097220370336</v>
       </c>
       <c r="I9">
-        <v>0.170351925390818</v>
+        <v>0.1721654299079403</v>
       </c>
       <c r="J9">
-        <v>0.21071427685814581</v>
+        <v>0.2116863637300102</v>
       </c>
       <c r="K9">
-        <v>0.36259046139074252</v>
+        <v>0.3644158392406011</v>
       </c>
       <c r="L9">
-        <v>0.37215394315042549</v>
+        <v>0.3800440761716107</v>
       </c>
       <c r="M9">
-        <v>0.41190037269540619</v>
+        <v>0.4157792172097211</v>
       </c>
       <c r="N9">
-        <v>0.44650609459698398</v>
+        <v>0.4481802000175921</v>
       </c>
       <c r="O9">
-        <v>0.452384646057432</v>
+        <v>0.4543067844441068</v>
       </c>
       <c r="P9">
-        <v>0.45166520338069682</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.457719294988321</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>-2.933955430439756E-2</v>
+        <v>-0.02866336127349795</v>
       </c>
       <c r="C10">
-        <v>-4.5054864233405691E-2</v>
+        <v>-0.04460708164022938</v>
       </c>
       <c r="D10">
-        <v>-0.11760495496627441</v>
+        <v>-0.1150810561837532</v>
       </c>
       <c r="E10">
-        <v>-0.13933366114944981</v>
+        <v>-0.1319697298468274</v>
       </c>
       <c r="F10">
-        <v>-8.7676285605281831E-2</v>
+        <v>-0.0753724711151416</v>
       </c>
       <c r="G10">
-        <v>1.0236348586471961E-2</v>
+        <v>0.006360993082261651</v>
       </c>
       <c r="H10">
-        <v>6.2538378961694133E-2</v>
+        <v>0.06310864494525159</v>
       </c>
       <c r="I10">
-        <v>0.16545625395496921</v>
+        <v>0.1624453984276476</v>
       </c>
       <c r="J10">
-        <v>0.1982177525341825</v>
+        <v>0.2021957335534782</v>
       </c>
       <c r="K10">
-        <v>0.35162161853709301</v>
+        <v>0.3566734188903294</v>
       </c>
       <c r="L10">
-        <v>0.3569414271810078</v>
+        <v>0.3584204150407703</v>
       </c>
       <c r="M10">
-        <v>0.39273398652653507</v>
+        <v>0.3991362255591526</v>
       </c>
       <c r="N10">
-        <v>0.42418834403990813</v>
+        <v>0.4362774875411413</v>
       </c>
       <c r="O10">
-        <v>0.4303324432236999</v>
+        <v>0.4388062275915379</v>
       </c>
       <c r="P10">
-        <v>0.43480954366284258</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.4454525475829365</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>-2.72134967200699E-2</v>
+        <v>-0.02769718729806322</v>
       </c>
       <c r="C11">
-        <v>-4.1010107181300201E-2</v>
+        <v>-0.04402667613135063</v>
       </c>
       <c r="D11">
-        <v>-0.11570669968391149</v>
+        <v>-0.1218938133269042</v>
       </c>
       <c r="E11">
-        <v>-0.13067948328676601</v>
+        <v>-0.1503995583198461</v>
       </c>
       <c r="F11">
-        <v>-8.3741829725959921E-2</v>
+        <v>-0.09663727050431177</v>
       </c>
       <c r="G11">
-        <v>1.043585673702481E-2</v>
+        <v>0.01338133318182724</v>
       </c>
       <c r="H11">
-        <v>6.1350736255529517E-2</v>
+        <v>0.05545259307247374</v>
       </c>
       <c r="I11">
-        <v>0.16242411002386781</v>
+        <v>0.1620163558978336</v>
       </c>
       <c r="J11">
-        <v>0.20071058617885301</v>
+        <v>0.2044144097546948</v>
       </c>
       <c r="K11">
-        <v>0.35894544342965068</v>
+        <v>0.3640778577246913</v>
       </c>
       <c r="L11">
-        <v>0.37523485905599713</v>
+        <v>0.3764665590004471</v>
       </c>
       <c r="M11">
-        <v>0.41714044193972483</v>
+        <v>0.4169423823363976</v>
       </c>
       <c r="N11">
-        <v>0.44457814108400417</v>
+        <v>0.4472034738357168</v>
       </c>
       <c r="O11">
-        <v>0.44841572820933973</v>
+        <v>0.4476922196627712</v>
       </c>
       <c r="P11">
-        <v>0.45403605954361542</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.4523534541194133</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>-2.450208730028337E-2</v>
+        <v>-0.02201577025580785</v>
       </c>
       <c r="C12">
-        <v>-7.0613642366767287E-2</v>
+        <v>-0.07430673468088028</v>
       </c>
       <c r="D12">
-        <v>-6.404545380959116E-2</v>
+        <v>-0.07561349098209226</v>
       </c>
       <c r="E12">
-        <v>-0.1214305105730024</v>
+        <v>-0.130940944733508</v>
       </c>
       <c r="F12">
-        <v>7.9183553173215043E-2</v>
+        <v>0.064408128350053</v>
       </c>
       <c r="G12">
-        <v>0.15193713094880981</v>
+        <v>0.1450106228145099</v>
       </c>
       <c r="H12">
-        <v>0.27017494184141472</v>
+        <v>0.26331349131969</v>
       </c>
       <c r="I12">
-        <v>0.35940235077819488</v>
+        <v>0.3631838351645765</v>
       </c>
       <c r="J12">
-        <v>0.40835053918095948</v>
+        <v>0.4103785254220804</v>
       </c>
       <c r="K12">
-        <v>0.43564653970414552</v>
+        <v>0.439958352367881</v>
       </c>
       <c r="L12">
-        <v>0.47235043052376979</v>
+        <v>0.4759218647209774</v>
       </c>
       <c r="M12">
-        <v>0.47490408266078171</v>
+        <v>0.4762214194306429</v>
       </c>
       <c r="N12">
-        <v>0.46006211150927201</v>
+        <v>0.4620176759196096</v>
       </c>
       <c r="O12">
-        <v>0.43762709008118988</v>
+        <v>0.4399373519631894</v>
       </c>
       <c r="P12">
-        <v>0.39711010613702069</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4022700692030778</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>-2.692605291563914E-2</v>
+        <v>-0.02871481678430841</v>
       </c>
       <c r="C13">
-        <v>-0.11591972004591949</v>
+        <v>-0.1191047761086555</v>
       </c>
       <c r="D13">
-        <v>-0.1116115935677893</v>
+        <v>-0.1166269199804432</v>
       </c>
       <c r="E13">
-        <v>-0.13286425832435231</v>
+        <v>-0.1347167804529344</v>
       </c>
       <c r="F13">
-        <v>-0.1689217214014585</v>
+        <v>-0.1673219192530294</v>
       </c>
       <c r="G13">
-        <v>-2.0994496331103871E-2</v>
+        <v>-0.01120796853540059</v>
       </c>
       <c r="H13">
-        <v>8.226235502524255E-3</v>
+        <v>0.01133049971278768</v>
       </c>
       <c r="I13">
-        <v>7.2203271849933096E-2</v>
+        <v>0.07601770138459801</v>
       </c>
       <c r="J13">
-        <v>0.16637849107278099</v>
+        <v>0.1548716441626851</v>
       </c>
       <c r="K13">
-        <v>0.24134142842219511</v>
+        <v>0.2371361715672821</v>
       </c>
       <c r="L13">
-        <v>0.25606326952919412</v>
+        <v>0.2462393433134994</v>
       </c>
       <c r="M13">
-        <v>0.27539630346548583</v>
+        <v>0.2651524645387868</v>
       </c>
       <c r="N13">
-        <v>0.28726596055518949</v>
+        <v>0.2730555803998256</v>
       </c>
       <c r="O13">
-        <v>0.29872781700592382</v>
+        <v>0.284548687721848</v>
       </c>
       <c r="P13">
-        <v>0.28009687571957842</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.26531516354822</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>-3.2174889823824208E-2</v>
+        <v>-0.033014167298918</v>
       </c>
       <c r="C14">
-        <v>-4.9726494695567523E-2</v>
+        <v>-0.04942454943857603</v>
       </c>
       <c r="D14">
-        <v>-0.13290386116263231</v>
+        <v>-0.1338161651621993</v>
       </c>
       <c r="E14">
-        <v>-0.1331537273146487</v>
+        <v>-0.1412826055214594</v>
       </c>
       <c r="F14">
-        <v>-0.17351621706193121</v>
+        <v>-0.1934404049802867</v>
       </c>
       <c r="G14">
-        <v>-0.1627776443083189</v>
+        <v>-0.1772380632462671</v>
       </c>
       <c r="H14">
-        <v>-1.8774890946375931E-2</v>
+        <v>-0.02936526123694279</v>
       </c>
       <c r="I14">
-        <v>9.9606915791608616E-2</v>
+        <v>0.08672961018097135</v>
       </c>
       <c r="J14">
-        <v>0.1005444751091944</v>
+        <v>0.08864325871547787</v>
       </c>
       <c r="K14">
-        <v>0.14362156067497769</v>
+        <v>0.13243454096521</v>
       </c>
       <c r="L14">
-        <v>0.24715186128845429</v>
+        <v>0.2395856993512682</v>
       </c>
       <c r="M14">
-        <v>0.36410786681315011</v>
+        <v>0.3512221473951909</v>
       </c>
       <c r="N14">
-        <v>0.40070970257965238</v>
+        <v>0.3900644987626132</v>
       </c>
       <c r="O14">
-        <v>0.43555774515086187</v>
+        <v>0.4213813440528286</v>
       </c>
       <c r="P14">
-        <v>0.45451723790752152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.4441903823316233</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>-3.5041258856454857E-2</v>
+        <v>-0.03688019357737708</v>
       </c>
       <c r="C15">
-        <v>-5.1849841689018683E-2</v>
+        <v>-0.05448857940665732</v>
       </c>
       <c r="D15">
-        <v>-0.1400295225467609</v>
+        <v>-0.1394815988172089</v>
       </c>
       <c r="E15">
-        <v>-0.143581340608436</v>
+        <v>-0.1437385967901639</v>
       </c>
       <c r="F15">
-        <v>-0.19380226285018179</v>
+        <v>-0.196567633189575</v>
       </c>
       <c r="G15">
-        <v>-0.16864494924165299</v>
+        <v>-0.1905324388589958</v>
       </c>
       <c r="H15">
-        <v>-2.968369690384727E-2</v>
+        <v>-0.03789493614196134</v>
       </c>
       <c r="I15">
-        <v>8.2915121513082446E-2</v>
+        <v>0.07772779884847242</v>
       </c>
       <c r="J15">
-        <v>8.127140198924912E-2</v>
+        <v>0.06626625802485696</v>
       </c>
       <c r="K15">
-        <v>0.13014569476800661</v>
+        <v>0.1247973312083399</v>
       </c>
       <c r="L15">
-        <v>0.2222568376297713</v>
+        <v>0.22869462668166</v>
       </c>
       <c r="M15">
-        <v>0.3406990416566813</v>
+        <v>0.3387334917315651</v>
       </c>
       <c r="N15">
-        <v>0.38543191967169871</v>
+        <v>0.3793227573013357</v>
       </c>
       <c r="O15">
-        <v>0.41876441811058951</v>
+        <v>0.4081491467212865</v>
       </c>
       <c r="P15">
-        <v>0.43284105906867443</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.4327442998264037</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>-3.116605603719903E-2</v>
+        <v>-0.03385294351654881</v>
       </c>
       <c r="C16">
-        <v>-4.8350967905297491E-2</v>
+        <v>-0.04751665261167776</v>
       </c>
       <c r="D16">
-        <v>-0.1386084736949742</v>
+        <v>-0.1298814709306268</v>
       </c>
       <c r="E16">
-        <v>-0.14359257737816361</v>
+        <v>-0.136262108252859</v>
       </c>
       <c r="F16">
-        <v>-0.19437540436073031</v>
+        <v>-0.1755901434039001</v>
       </c>
       <c r="G16">
-        <v>-0.18403536945316271</v>
+        <v>-0.1727221148170787</v>
       </c>
       <c r="H16">
-        <v>-3.4561961147216151E-2</v>
+        <v>-0.03341884494458229</v>
       </c>
       <c r="I16">
-        <v>7.5824090981041425E-2</v>
+        <v>0.08641772015822323</v>
       </c>
       <c r="J16">
-        <v>7.9061757199418173E-2</v>
+        <v>0.08668707066648144</v>
       </c>
       <c r="K16">
-        <v>0.1251979544919542</v>
+        <v>0.1337698633383409</v>
       </c>
       <c r="L16">
-        <v>0.22327619468751661</v>
+        <v>0.2314372544802493</v>
       </c>
       <c r="M16">
-        <v>0.34204424492297247</v>
+        <v>0.3465524716213722</v>
       </c>
       <c r="N16">
-        <v>0.38404847880428361</v>
+        <v>0.393852363926615</v>
       </c>
       <c r="O16">
-        <v>0.42024532730497499</v>
+        <v>0.4282383902507738</v>
       </c>
       <c r="P16">
-        <v>0.44632830684694358</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.444288408115127</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>-3.0265396613072929E-2</v>
+        <v>-0.03056041754341425</v>
       </c>
       <c r="C17">
-        <v>-4.7213253615531463E-2</v>
+        <v>-0.04983270458941524</v>
       </c>
       <c r="D17">
-        <v>-0.1349473489186224</v>
+        <v>-0.136308512687793</v>
       </c>
       <c r="E17">
-        <v>-0.14335708168608841</v>
+        <v>-0.138386091441607</v>
       </c>
       <c r="F17">
-        <v>-0.185809940175337</v>
+        <v>-0.1759887451036491</v>
       </c>
       <c r="G17">
-        <v>-0.17533913755622399</v>
+        <v>-0.1735594837073961</v>
       </c>
       <c r="H17">
-        <v>-3.7645397217738463E-2</v>
+        <v>-0.03067260174656454</v>
       </c>
       <c r="I17">
-        <v>6.884894276424075E-2</v>
+        <v>0.07741805991573414</v>
       </c>
       <c r="J17">
-        <v>5.9995046940667721E-2</v>
+        <v>0.07107962836468631</v>
       </c>
       <c r="K17">
-        <v>0.10244677037051959</v>
+        <v>0.1156275395874102</v>
       </c>
       <c r="L17">
-        <v>0.19314401574209239</v>
+        <v>0.2013818318796746</v>
       </c>
       <c r="M17">
-        <v>0.30616139125010439</v>
+        <v>0.3101255585905598</v>
       </c>
       <c r="N17">
-        <v>0.35402690049053198</v>
+        <v>0.3502054877422179</v>
       </c>
       <c r="O17">
-        <v>0.39686951934954962</v>
+        <v>0.390271547401998</v>
       </c>
       <c r="P17">
-        <v>0.42211673842806979</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.4145873933533699</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-2.4217991646950938E-2</v>
+        <v>-0.0226674083076379</v>
       </c>
       <c r="C18">
-        <v>-7.3948185866960961E-2</v>
+        <v>-0.07632034796402629</v>
       </c>
       <c r="D18">
-        <v>-7.0844677528151712E-2</v>
+        <v>-0.08097014696231396</v>
       </c>
       <c r="E18">
-        <v>-0.13814266259765789</v>
+        <v>-0.1391488661092355</v>
       </c>
       <c r="F18">
-        <v>7.6094396821352467E-2</v>
+        <v>0.08529751765163408</v>
       </c>
       <c r="G18">
-        <v>0.19313826540512419</v>
+        <v>0.1949474115686936</v>
       </c>
       <c r="H18">
-        <v>0.25152074030285471</v>
+        <v>0.2555628148670935</v>
       </c>
       <c r="I18">
-        <v>0.35048601228540788</v>
+        <v>0.3517801075411581</v>
       </c>
       <c r="J18">
-        <v>0.40935832204875888</v>
+        <v>0.4088598842132198</v>
       </c>
       <c r="K18">
-        <v>0.43219273475162562</v>
+        <v>0.4275777662582173</v>
       </c>
       <c r="L18">
-        <v>0.46097058648735117</v>
+        <v>0.4586363551542268</v>
       </c>
       <c r="M18">
-        <v>0.46423628573757753</v>
+        <v>0.4648382889697032</v>
       </c>
       <c r="N18">
-        <v>0.43828471985305828</v>
+        <v>0.4381102729209496</v>
       </c>
       <c r="O18">
-        <v>0.41411436738852281</v>
+        <v>0.4127911731198863</v>
       </c>
       <c r="P18">
-        <v>0.40155528587779332</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.3956724611265258</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>-2.611742810668264E-2</v>
+        <v>-0.0248550799648685</v>
       </c>
       <c r="C19">
-        <v>-8.5120073876420302E-2</v>
+        <v>-0.08162533638583823</v>
       </c>
       <c r="D19">
-        <v>-9.3690315539708038E-2</v>
+        <v>-0.08904660885249449</v>
       </c>
       <c r="E19">
-        <v>-8.1912722540106078E-2</v>
+        <v>-0.09584444319337346</v>
       </c>
       <c r="F19">
-        <v>0.13979114010134361</v>
+        <v>0.1427433825709921</v>
       </c>
       <c r="G19">
-        <v>0.27521468228575718</v>
+        <v>0.2667403159834129</v>
       </c>
       <c r="H19">
-        <v>0.32259726547499767</v>
+        <v>0.3192126083969888</v>
       </c>
       <c r="I19">
-        <v>0.39992059382430722</v>
+        <v>0.3957326861958314</v>
       </c>
       <c r="J19">
-        <v>0.44904534634189858</v>
+        <v>0.4420997467347939</v>
       </c>
       <c r="K19">
-        <v>0.46818093951348638</v>
+        <v>0.4625459782102323</v>
       </c>
       <c r="L19">
-        <v>0.483109521902365</v>
+        <v>0.4823262541897742</v>
       </c>
       <c r="M19">
-        <v>0.48566453275073351</v>
+        <v>0.4868281693384465</v>
       </c>
       <c r="N19">
-        <v>0.47720595548016759</v>
+        <v>0.4810826852982877</v>
       </c>
       <c r="O19">
-        <v>0.48632080053751298</v>
+        <v>0.4853215110979693</v>
       </c>
       <c r="P19">
-        <v>0.48430354896239702</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.479059385546237</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>-2.5012669672330179E-2</v>
+        <v>-0.02366993559661576</v>
       </c>
       <c r="C20">
-        <v>-5.9310275032019903E-2</v>
+        <v>-0.05289006852313399</v>
       </c>
       <c r="D20">
-        <v>-8.5457088534716577E-2</v>
+        <v>-0.08929995238558594</v>
       </c>
       <c r="E20">
-        <v>1.2280023059936611E-2</v>
+        <v>0.007922172863827437</v>
       </c>
       <c r="F20">
-        <v>0.18164999426366829</v>
+        <v>0.1692404474038029</v>
       </c>
       <c r="G20">
-        <v>0.215599847508786</v>
+        <v>0.1980345152958766</v>
       </c>
       <c r="H20">
-        <v>0.31296179618754499</v>
+        <v>0.2979442829870516</v>
       </c>
       <c r="I20">
-        <v>0.38122814564685842</v>
+        <v>0.3738467579066261</v>
       </c>
       <c r="J20">
-        <v>0.41756167895271468</v>
+        <v>0.41223128393061</v>
       </c>
       <c r="K20">
-        <v>0.46663396049694711</v>
+        <v>0.4585111233697267</v>
       </c>
       <c r="L20">
-        <v>0.48516952569568422</v>
+        <v>0.4771942045376036</v>
       </c>
       <c r="M20">
-        <v>0.46970153865644781</v>
-      </c>
-      <c r="N20" s="2">
-        <v>0.51917692080955913</v>
+        <v>0.463953960320541</v>
+      </c>
+      <c r="N20">
+        <v>0.5142626573557766</v>
       </c>
       <c r="O20">
-        <v>0.51519735729869121</v>
+        <v>0.5095296781421683</v>
       </c>
       <c r="P20">
-        <v>0.51244004449616165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.5009982939072178</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>-2.1948876945306232E-2</v>
+        <v>-0.0205698904552352</v>
       </c>
       <c r="C21">
-        <v>-3.7159428544228733E-2</v>
+        <v>-0.03846214656275225</v>
       </c>
       <c r="D21">
-        <v>-0.13892133216990421</v>
+        <v>-0.1529007092681984</v>
       </c>
       <c r="E21">
-        <v>3.1442242006781161E-2</v>
+        <v>0.01194369549715431</v>
       </c>
       <c r="F21">
-        <v>0.1000165049259589</v>
+        <v>0.09040084456202027</v>
       </c>
       <c r="G21">
-        <v>0.13273780892895559</v>
+        <v>0.1266269742124849</v>
       </c>
       <c r="H21">
-        <v>0.17425825142420709</v>
+        <v>0.171535502200363</v>
       </c>
       <c r="I21">
-        <v>0.23043466780368199</v>
+        <v>0.210878844775751</v>
       </c>
       <c r="J21">
-        <v>0.29775081328228498</v>
+        <v>0.2961568981693292</v>
       </c>
       <c r="K21">
-        <v>0.33991470446448729</v>
+        <v>0.335228484302531</v>
       </c>
       <c r="L21">
-        <v>0.36142903810093158</v>
+        <v>0.3575726139428385</v>
       </c>
       <c r="M21">
-        <v>0.34782298525947591</v>
+        <v>0.3477014081003212</v>
       </c>
       <c r="N21">
-        <v>0.31795713535567199</v>
+        <v>0.3231851855999194</v>
       </c>
       <c r="O21">
-        <v>0.3077278612917686</v>
+        <v>0.311921706096718</v>
       </c>
       <c r="P21">
-        <v>0.31744622066892331</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.3240716900144358</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>-1.7910527651347961E-2</v>
+        <v>-0.02165295856754031</v>
       </c>
       <c r="C22">
-        <v>-3.6535020339945379E-2</v>
+        <v>-0.04033466327126745</v>
       </c>
       <c r="D22">
-        <v>-0.1356405934864913</v>
+        <v>-0.146490266628592</v>
       </c>
       <c r="E22">
-        <v>3.5617715479093918E-2</v>
+        <v>0.02982315398268879</v>
       </c>
       <c r="F22">
-        <v>0.1083534347685446</v>
+        <v>0.09788069805077736</v>
       </c>
       <c r="G22">
-        <v>0.12691199002011699</v>
+        <v>0.1226125206553352</v>
       </c>
       <c r="H22">
-        <v>0.15394182290976521</v>
+        <v>0.1492975407677374</v>
       </c>
       <c r="I22">
-        <v>0.1848347930573844</v>
+        <v>0.172053346286706</v>
       </c>
       <c r="J22">
-        <v>0.26765998980027988</v>
+        <v>0.2573578131377989</v>
       </c>
       <c r="K22">
-        <v>0.3086259592591149</v>
+        <v>0.2920314298695409</v>
       </c>
       <c r="L22">
-        <v>0.32523936171137119</v>
+        <v>0.306270313911125</v>
       </c>
       <c r="M22">
-        <v>0.32723402802963908</v>
+        <v>0.3100115922725679</v>
       </c>
       <c r="N22">
-        <v>0.31919563243997567</v>
+        <v>0.3012406652471075</v>
       </c>
       <c r="O22">
-        <v>0.3179734108487679</v>
+        <v>0.2983424163234177</v>
       </c>
       <c r="P22">
-        <v>0.31612786125581638</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.2942345940888458</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>-2.258099459805744E-2</v>
+        <v>-0.01906016357514158</v>
       </c>
       <c r="C23">
-        <v>-8.7505345737759505E-2</v>
+        <v>-0.08776920225960347</v>
       </c>
       <c r="D23">
-        <v>4.6909938502970733E-2</v>
+        <v>0.06389520843593094</v>
       </c>
       <c r="E23">
-        <v>0.11041427123680859</v>
+        <v>0.1173658326412301</v>
       </c>
       <c r="F23">
-        <v>0.28262405752233849</v>
+        <v>0.2891305837625077</v>
       </c>
       <c r="G23">
-        <v>0.37116853912353742</v>
+        <v>0.3781610403437616</v>
       </c>
       <c r="H23">
-        <v>0.41141148657236631</v>
+        <v>0.4170614355581234</v>
       </c>
       <c r="I23">
-        <v>0.44104105794042531</v>
+        <v>0.4480213723429537</v>
       </c>
       <c r="J23">
-        <v>0.46963533397791007</v>
+        <v>0.4726251136447324</v>
       </c>
       <c r="K23">
-        <v>0.47789552535474061</v>
+        <v>0.4743426615402531</v>
       </c>
       <c r="L23">
-        <v>0.47806134495154162</v>
+        <v>0.4713507364483198</v>
       </c>
       <c r="M23">
-        <v>0.45335771059219071</v>
+        <v>0.4464887329187834</v>
       </c>
       <c r="N23">
-        <v>0.44107359903196403</v>
+        <v>0.4352375140923365</v>
       </c>
       <c r="O23">
-        <v>0.42891782921642541</v>
+        <v>0.4192497752670303</v>
       </c>
       <c r="P23">
-        <v>0.39837199825726261</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.3925506225832374</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>-6.6483370787846968E-2</v>
+        <v>-0.06949627022102059</v>
       </c>
       <c r="C24">
-        <v>-2.3405525455163479E-3</v>
+        <v>-0.004338283974481131</v>
       </c>
       <c r="D24">
-        <v>2.548286000812883E-2</v>
+        <v>0.01562968123723775</v>
       </c>
       <c r="E24">
-        <v>1.058719730339145E-2</v>
+        <v>0.00179868509105211</v>
       </c>
       <c r="F24">
-        <v>-4.1081001899427053E-2</v>
+        <v>-0.04822407335791346</v>
       </c>
       <c r="G24">
-        <v>-0.10853801317581969</v>
+        <v>-0.1221385868053295</v>
       </c>
       <c r="H24">
-        <v>-8.8925037692114503E-2</v>
+        <v>-0.09995139933197521</v>
       </c>
       <c r="I24">
-        <v>-9.6647462927662797E-2</v>
+        <v>-0.1103401384903305</v>
       </c>
       <c r="J24">
-        <v>-0.1811941507475556</v>
+        <v>-0.1901370136632914</v>
       </c>
       <c r="K24">
-        <v>-0.31988538384180221</v>
+        <v>-0.333384950037483</v>
       </c>
       <c r="L24">
-        <v>-0.32503629693316322</v>
+        <v>-0.3474115673402116</v>
       </c>
       <c r="M24">
-        <v>-0.35846783055190401</v>
+        <v>-0.3805542109803519</v>
       </c>
       <c r="N24">
-        <v>-0.41023214562383509</v>
+        <v>-0.4453510678172998</v>
       </c>
       <c r="O24">
-        <v>-0.49003285738061719</v>
+        <v>-0.5105336010998784</v>
       </c>
       <c r="P24">
-        <v>-0.57961161790697191</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>-0.5911555890520964</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-0.26463687606075897</v>
+        <v>-0.2583430517767426</v>
       </c>
       <c r="C25">
-        <v>-0.16484018650588489</v>
+        <v>-0.1566754938370986</v>
       </c>
       <c r="D25">
-        <v>-0.11312908611418671</v>
+        <v>-0.1076704839349962</v>
       </c>
       <c r="E25">
-        <v>-9.0379084156550035E-2</v>
+        <v>-0.08862161893716981</v>
       </c>
       <c r="F25">
-        <v>-0.1993173499552012</v>
+        <v>-0.1899631945584164</v>
       </c>
       <c r="G25">
-        <v>-0.24953966628252999</v>
+        <v>-0.2384205929221173</v>
       </c>
       <c r="H25">
-        <v>-0.25478141566789181</v>
+        <v>-0.2426131543421367</v>
       </c>
       <c r="I25">
-        <v>-0.21526114613196221</v>
+        <v>-0.2067698383446986</v>
       </c>
       <c r="J25">
-        <v>-0.224147074652707</v>
+        <v>-0.2237382482103365</v>
       </c>
       <c r="K25">
-        <v>-0.30221244680634302</v>
+        <v>-0.3106552523148586</v>
       </c>
       <c r="L25">
-        <v>-0.33845967426361512</v>
+        <v>-0.3510889005238125</v>
       </c>
       <c r="M25">
-        <v>-0.44564585556426373</v>
+        <v>-0.4585189727970073</v>
       </c>
       <c r="N25">
-        <v>-0.53570348689262004</v>
+        <v>-0.5564534641182666</v>
       </c>
       <c r="O25">
-        <v>-0.58592703909471289</v>
+        <v>-0.6058272786950106</v>
       </c>
       <c r="P25">
-        <v>-0.62206147869637618</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>-0.6252563631655124</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>-8.6200703061535475E-2</v>
+        <v>-0.0839221464753326</v>
       </c>
       <c r="C26">
-        <v>2.6919841001722469E-3</v>
+        <v>0.006437852675554847</v>
       </c>
       <c r="D26">
-        <v>4.2459007690081263E-2</v>
+        <v>0.03983831611714622</v>
       </c>
       <c r="E26">
-        <v>7.1086912782973383E-2</v>
+        <v>0.07004994796919847</v>
       </c>
       <c r="F26">
-        <v>6.7401411340717934E-2</v>
+        <v>0.06517887033730711</v>
       </c>
       <c r="G26">
-        <v>0.11053459012041721</v>
+        <v>0.1038146701557488</v>
       </c>
       <c r="H26">
-        <v>0.11992218573428159</v>
+        <v>0.1146630030608124</v>
       </c>
       <c r="I26">
-        <v>0.1113856826189705</v>
+        <v>0.1107674359575307</v>
       </c>
       <c r="J26">
-        <v>0.12807322097325891</v>
+        <v>0.1274161936207352</v>
       </c>
       <c r="K26">
-        <v>0.12961087661677551</v>
+        <v>0.1373979634662869</v>
       </c>
       <c r="L26">
-        <v>9.9888351978238088E-2</v>
+        <v>0.1090555561047262</v>
       </c>
       <c r="M26">
-        <v>8.8902564659424116E-2</v>
+        <v>0.09211447718968319</v>
       </c>
       <c r="N26">
-        <v>5.5323431991093221E-2</v>
+        <v>0.05953964632567278</v>
       </c>
       <c r="O26">
-        <v>1.65996276721922E-2</v>
+        <v>0.02591590241201679</v>
       </c>
       <c r="P26">
-        <v>-2.0505984286104659E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>-0.01310730404467172</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>-0.10196023726711841</v>
+        <v>-0.1040296974902475</v>
       </c>
       <c r="C27">
-        <v>-2.615197346632972E-2</v>
+        <v>-0.02500985723389105</v>
       </c>
       <c r="D27">
-        <v>6.4136522120668199E-2</v>
+        <v>0.07288604337684268</v>
       </c>
       <c r="E27">
-        <v>0.1037248416526208</v>
+        <v>0.09551600251676144</v>
       </c>
       <c r="F27">
-        <v>6.4961569812645614E-2</v>
+        <v>0.06361416941514693</v>
       </c>
       <c r="G27">
-        <v>6.3653644913777521E-2</v>
+        <v>0.06185156010289651</v>
       </c>
       <c r="H27">
-        <v>4.4398401110197737E-2</v>
+        <v>0.04163502047190994</v>
       </c>
       <c r="I27">
-        <v>-3.4371717448431802E-2</v>
+        <v>-0.03076134415629339</v>
       </c>
       <c r="J27">
-        <v>-1.1830035111010511E-2</v>
+        <v>-0.01546308073358554</v>
       </c>
       <c r="K27">
-        <v>-9.6804294250068428E-4</v>
+        <v>-0.00576167045417045</v>
       </c>
       <c r="L27">
-        <v>3.1000107250052759E-2</v>
+        <v>0.02348242087722173</v>
       </c>
       <c r="M27">
-        <v>4.845765322455698E-2</v>
+        <v>0.0398647849092462</v>
       </c>
       <c r="N27">
-        <v>4.2026692148452081E-2</v>
+        <v>0.03666277090350639</v>
       </c>
       <c r="O27">
-        <v>-1.9280306327138039E-2</v>
+        <v>-0.02824784164257134</v>
       </c>
       <c r="P27">
-        <v>-6.9812920983227389E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>-0.07582142370020066</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>-3.7135902894754783E-2</v>
+        <v>-0.03655537853962401</v>
       </c>
       <c r="C28">
-        <v>-0.13945279769906749</v>
+        <v>-0.1379603409380777</v>
       </c>
       <c r="D28">
-        <v>-0.15351762402452401</v>
+        <v>-0.1562057346036211</v>
       </c>
       <c r="E28">
-        <v>-0.1249573469754677</v>
+        <v>-0.1278949530088566</v>
       </c>
       <c r="F28">
-        <v>-0.12670692830072511</v>
+        <v>-0.1315547292904225</v>
       </c>
       <c r="G28">
-        <v>-5.5564151475022777E-2</v>
+        <v>-0.0559316362213273</v>
       </c>
       <c r="H28">
-        <v>-0.13802970043283139</v>
+        <v>-0.124326610391878</v>
       </c>
       <c r="I28">
-        <v>-3.8510988526661107E-2</v>
+        <v>-0.03847781655264771</v>
       </c>
       <c r="J28">
-        <v>0.13642115353161391</v>
+        <v>0.12914463467778</v>
       </c>
       <c r="K28">
-        <v>0.21281782751617959</v>
+        <v>0.2217238603036982</v>
       </c>
       <c r="L28">
-        <v>0.25997973938603358</v>
+        <v>0.2611084142165482</v>
       </c>
       <c r="M28">
-        <v>0.2419260129073795</v>
+        <v>0.2382999989415901</v>
       </c>
       <c r="N28">
-        <v>0.1760870565500649</v>
+        <v>0.1695846182240736</v>
       </c>
       <c r="O28">
-        <v>0.12517487619269799</v>
+        <v>0.1214417563471944</v>
       </c>
       <c r="P28">
-        <v>5.2141653559584368E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.04342956860031854</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-4.1095347417710953E-2</v>
+        <v>-0.04030139197953295</v>
       </c>
       <c r="C29">
-        <v>-0.148977618233155</v>
+        <v>-0.1469188028521679</v>
       </c>
       <c r="D29">
-        <v>-0.15723752491838841</v>
+        <v>-0.1554252169855284</v>
       </c>
       <c r="E29">
-        <v>-0.120918395852707</v>
+        <v>-0.1176849214281242</v>
       </c>
       <c r="F29">
-        <v>-0.10992288327497431</v>
+        <v>-0.1109025696496925</v>
       </c>
       <c r="G29">
-        <v>-8.8174394317164687E-2</v>
+        <v>-0.09050104415533768</v>
       </c>
       <c r="H29">
-        <v>-0.16683579625585121</v>
+        <v>-0.1659582073535472</v>
       </c>
       <c r="I29">
-        <v>-0.1193051078005434</v>
+        <v>-0.09690093678556788</v>
       </c>
       <c r="J29">
-        <v>-1.776154807108106E-2</v>
+        <v>-0.01794449358959583</v>
       </c>
       <c r="K29">
-        <v>0.18891025785406401</v>
+        <v>0.1879528873481787</v>
       </c>
       <c r="L29">
-        <v>0.2254284727880573</v>
+        <v>0.2215732239682137</v>
       </c>
       <c r="M29">
-        <v>0.24865288296255619</v>
+        <v>0.2508960849237442</v>
       </c>
       <c r="N29">
-        <v>0.21853241787428651</v>
+        <v>0.2176819837218386</v>
       </c>
       <c r="O29">
-        <v>0.1624135339235554</v>
+        <v>0.1672832672493955</v>
       </c>
       <c r="P29">
-        <v>0.1071173008392155</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.1078084544016726</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-3.8277785247426623E-2</v>
+        <v>-0.03620090780551077</v>
       </c>
       <c r="C30">
-        <v>-0.15280789778468451</v>
+        <v>-0.1480811705231677</v>
       </c>
       <c r="D30">
-        <v>-0.1324599410802412</v>
+        <v>-0.1256568238832053</v>
       </c>
       <c r="E30">
-        <v>-9.1744830020134102E-2</v>
+        <v>-0.08306043128572031</v>
       </c>
       <c r="F30">
-        <v>-0.1238664483895872</v>
+        <v>-0.1285681321725141</v>
       </c>
       <c r="G30">
-        <v>-9.2815845515729342E-2</v>
+        <v>-0.09773952707504145</v>
       </c>
       <c r="H30">
-        <v>3.571437585059007E-2</v>
+        <v>0.02726915234701851</v>
       </c>
       <c r="I30">
-        <v>-1.9486974694881479E-2</v>
+        <v>-0.02818737956976503</v>
       </c>
       <c r="J30">
-        <v>0.1325006231704772</v>
+        <v>0.1212290350268405</v>
       </c>
       <c r="K30">
-        <v>0.21712533723917629</v>
+        <v>0.2120546509401655</v>
       </c>
       <c r="L30">
-        <v>0.2109761579143897</v>
+        <v>0.2145614667769675</v>
       </c>
       <c r="M30">
-        <v>0.18898445747558151</v>
+        <v>0.1974909027126291</v>
       </c>
       <c r="N30">
-        <v>0.14662025750785801</v>
+        <v>0.1590585085271485</v>
       </c>
       <c r="O30">
-        <v>9.7550883651750672E-2</v>
+        <v>0.1043490735310293</v>
       </c>
       <c r="P30">
-        <v>2.769097379186046E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.02991648711076273</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>-3.4550697773512842E-2</v>
+        <v>-0.03989862643544272</v>
       </c>
       <c r="C31">
-        <v>-0.14825944745968919</v>
+        <v>-0.1518112315653981</v>
       </c>
       <c r="D31">
-        <v>-0.13000979615335501</v>
+        <v>-0.1338957677378812</v>
       </c>
       <c r="E31">
-        <v>-8.1530937497903452E-2</v>
+        <v>-0.0864384325116164</v>
       </c>
       <c r="F31">
-        <v>-0.11814511136156811</v>
+        <v>-0.1192510163779714</v>
       </c>
       <c r="G31">
-        <v>-9.0027281236235782E-2</v>
+        <v>-0.09450949721119646</v>
       </c>
       <c r="H31">
-        <v>2.1515857426492129E-2</v>
+        <v>0.01682253807270365</v>
       </c>
       <c r="I31">
-        <v>-2.337786238039748E-2</v>
+        <v>-0.03814067753505404</v>
       </c>
       <c r="J31">
-        <v>0.10552506603748781</v>
+        <v>0.1003362601835343</v>
       </c>
       <c r="K31">
-        <v>0.24803561163266821</v>
+        <v>0.2509716518112528</v>
       </c>
       <c r="L31">
-        <v>0.28455212879356739</v>
+        <v>0.2902737486496172</v>
       </c>
       <c r="M31">
-        <v>0.29854811418765148</v>
+        <v>0.302446066930601</v>
       </c>
       <c r="N31">
-        <v>0.29845567332618278</v>
+        <v>0.3047525315274562</v>
       </c>
       <c r="O31">
-        <v>0.27298577190771273</v>
+        <v>0.2873134990890823</v>
       </c>
       <c r="P31">
-        <v>0.26213404277957952</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.2779814584931902</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>-3.8549516503128649E-2</v>
+        <v>-0.0374511855043921</v>
       </c>
       <c r="C32">
-        <v>-0.14591002253863911</v>
+        <v>-0.1418128447619317</v>
       </c>
       <c r="D32">
-        <v>-0.15751339833654579</v>
+        <v>-0.1539841879134369</v>
       </c>
       <c r="E32">
-        <v>-0.1233186055757672</v>
+        <v>-0.1177833549718022</v>
       </c>
       <c r="F32">
-        <v>-0.1144047612887762</v>
+        <v>-0.1087586218372775</v>
       </c>
       <c r="G32">
-        <v>-9.5656060866400563E-2</v>
+        <v>-0.0911558717422651</v>
       </c>
       <c r="H32">
-        <v>-0.15426778677172501</v>
+        <v>-0.1434248502133228</v>
       </c>
       <c r="I32">
-        <v>-0.12444167722657409</v>
+        <v>-0.1232024595211451</v>
       </c>
       <c r="J32">
-        <v>-4.1981842217019623E-2</v>
+        <v>-0.04646328923029547</v>
       </c>
       <c r="K32">
-        <v>0.1892196938620492</v>
+        <v>0.1900656885014933</v>
       </c>
       <c r="L32">
-        <v>0.25530098227936382</v>
+        <v>0.2589848795812969</v>
       </c>
       <c r="M32">
-        <v>0.26841998042916188</v>
+        <v>0.2736471227418768</v>
       </c>
       <c r="N32">
-        <v>0.27030465150354072</v>
+        <v>0.2825759093545233</v>
       </c>
       <c r="O32">
-        <v>0.25404188194929322</v>
+        <v>0.259287924861898</v>
       </c>
       <c r="P32">
-        <v>0.24993753304085661</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.2617767774258864</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>-4.2215718612463107E-2</v>
+        <v>-0.03855100065843783</v>
       </c>
       <c r="C33">
-        <v>-0.14877461499820149</v>
+        <v>-0.1458364203379819</v>
       </c>
       <c r="D33">
-        <v>-0.1593950975697068</v>
+        <v>-0.1554155068385158</v>
       </c>
       <c r="E33">
-        <v>-0.12067151294925189</v>
+        <v>-0.1189435655417459</v>
       </c>
       <c r="F33">
-        <v>-0.11049180439299421</v>
+        <v>-0.1092853732113765</v>
       </c>
       <c r="G33">
-        <v>-9.1453470064970857E-2</v>
+        <v>-0.08835563322375663</v>
       </c>
       <c r="H33">
-        <v>-0.1551725899649562</v>
+        <v>-0.1425126700534693</v>
       </c>
       <c r="I33">
-        <v>-0.1143034599191755</v>
+        <v>-0.1142866097231656</v>
       </c>
       <c r="J33">
-        <v>-3.8821698820818443E-2</v>
+        <v>-0.04190825149312326</v>
       </c>
       <c r="K33">
-        <v>0.20821074994041361</v>
+        <v>0.2152377964582237</v>
       </c>
       <c r="L33">
-        <v>0.26912449910322628</v>
+        <v>0.2689821499900757</v>
       </c>
       <c r="M33">
-        <v>0.29167440882275891</v>
+        <v>0.287075640589031</v>
       </c>
       <c r="N33">
-        <v>0.29873171593737702</v>
+        <v>0.297862610154289</v>
       </c>
       <c r="O33">
-        <v>0.28636997558310001</v>
+        <v>0.2915081816260456</v>
       </c>
       <c r="P33">
-        <v>0.29264876175482279</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.2970764390346991</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>-3.8062659424498782E-2</v>
+        <v>-0.0389621098644793</v>
       </c>
       <c r="C34">
-        <v>-0.14576396304047939</v>
+        <v>-0.1427932469980006</v>
       </c>
       <c r="D34">
-        <v>-0.15559168098442319</v>
+        <v>-0.1543836123777532</v>
       </c>
       <c r="E34">
-        <v>-0.1217970032684723</v>
+        <v>-0.1195624430288047</v>
       </c>
       <c r="F34">
-        <v>-0.1153357130674839</v>
+        <v>-0.1074766133790956</v>
       </c>
       <c r="G34">
-        <v>-9.4245176342733258E-2</v>
+        <v>-0.08264000811508507</v>
       </c>
       <c r="H34">
-        <v>-0.1457387711293936</v>
+        <v>-0.1382879366478705</v>
       </c>
       <c r="I34">
-        <v>-0.12577841622383529</v>
+        <v>-0.1253101007328185</v>
       </c>
       <c r="J34">
-        <v>-5.2870858380747413E-2</v>
+        <v>-0.0509471239179546</v>
       </c>
       <c r="K34">
-        <v>0.20221039015024611</v>
+        <v>0.206070214879192</v>
       </c>
       <c r="L34">
-        <v>0.24958184191539509</v>
+        <v>0.2567120358570066</v>
       </c>
       <c r="M34">
-        <v>0.27797963670063719</v>
+        <v>0.2771981279451426</v>
       </c>
       <c r="N34">
-        <v>0.28365976217321609</v>
+        <v>0.2767301747863536</v>
       </c>
       <c r="O34">
-        <v>0.26709036952958909</v>
+        <v>0.2807382162595561</v>
       </c>
       <c r="P34">
-        <v>0.27748492072954328</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2785786803000883</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>-4.5706851011120132E-2</v>
+        <v>-0.04101509217535057</v>
       </c>
       <c r="C35">
-        <v>-0.1492863230018722</v>
+        <v>-0.1469620907016318</v>
       </c>
       <c r="D35">
-        <v>-0.1637289186027906</v>
+        <v>-0.16320853637771</v>
       </c>
       <c r="E35">
-        <v>-0.1310320358535241</v>
+        <v>-0.1250263332965265</v>
       </c>
       <c r="F35">
-        <v>-0.1246570289204436</v>
+        <v>-0.1167192117371241</v>
       </c>
       <c r="G35">
-        <v>-9.9373257318332964E-2</v>
+        <v>-0.09607719887167776</v>
       </c>
       <c r="H35">
-        <v>-0.15188016858178419</v>
+        <v>-0.1598080929976638</v>
       </c>
       <c r="I35">
-        <v>-0.1363316461969353</v>
+        <v>-0.1468917241049291</v>
       </c>
       <c r="J35">
-        <v>-7.4572155766761336E-2</v>
+        <v>-0.07984708411033492</v>
       </c>
       <c r="K35">
-        <v>0.18113671925181241</v>
+        <v>0.17663947493598</v>
       </c>
       <c r="L35">
-        <v>0.23785643003038379</v>
+        <v>0.2338593967521249</v>
       </c>
       <c r="M35">
-        <v>0.26388818562755179</v>
+        <v>0.2644692177178044</v>
       </c>
       <c r="N35">
-        <v>0.28194496463759672</v>
+        <v>0.2825505104338115</v>
       </c>
       <c r="O35">
-        <v>0.27783223567952531</v>
+        <v>0.2783774408157993</v>
       </c>
       <c r="P35">
-        <v>0.29747750612273283</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.2976311848615343</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>-3.9686781104404788E-2</v>
+        <v>-0.0414638806154648</v>
       </c>
       <c r="C36">
-        <v>-0.14216816468728591</v>
+        <v>-0.1506406359388672</v>
       </c>
       <c r="D36">
-        <v>-0.1545176642390054</v>
+        <v>-0.1616094968996717</v>
       </c>
       <c r="E36">
-        <v>-0.1170957061564251</v>
+        <v>-0.123184715667589</v>
       </c>
       <c r="F36">
-        <v>-0.1089123443066464</v>
+        <v>-0.1183373584005359</v>
       </c>
       <c r="G36">
-        <v>-9.010836347925695E-2</v>
+        <v>-0.0981765182965328</v>
       </c>
       <c r="H36">
-        <v>-0.15135410960229159</v>
+        <v>-0.1542454245552607</v>
       </c>
       <c r="I36">
-        <v>-0.1128660136976221</v>
+        <v>-0.1252287271071075</v>
       </c>
       <c r="J36">
-        <v>-3.3873374063677991E-2</v>
+        <v>-0.04947316339679262</v>
       </c>
       <c r="K36">
-        <v>0.2001346554543581</v>
+        <v>0.1903607909678932</v>
       </c>
       <c r="L36">
-        <v>0.25430304809743581</v>
+        <v>0.2556031419340437</v>
       </c>
       <c r="M36">
-        <v>0.27114314704334602</v>
+        <v>0.2817982232741989</v>
       </c>
       <c r="N36">
-        <v>0.26603311221792769</v>
+        <v>0.2700978137471752</v>
       </c>
       <c r="O36">
-        <v>0.23487703892127601</v>
+        <v>0.2396085918653446</v>
       </c>
       <c r="P36">
-        <v>0.2207974090115741</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.2236310558276528</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>-3.5774829525836223E-2</v>
+        <v>-0.03921919772846619</v>
       </c>
       <c r="C37">
-        <v>-0.14026064393517679</v>
+        <v>-0.137480108531141</v>
       </c>
       <c r="D37">
-        <v>-0.15244714960864739</v>
+        <v>-0.1475156027379284</v>
       </c>
       <c r="E37">
-        <v>-0.1203861060512066</v>
+        <v>-0.1127772008167578</v>
       </c>
       <c r="F37">
-        <v>-0.111051558457666</v>
+        <v>-0.1054002581183461</v>
       </c>
       <c r="G37">
-        <v>-8.7629209277960377E-2</v>
+        <v>-0.08072847883149102</v>
       </c>
       <c r="H37">
-        <v>-0.15673192378541961</v>
+        <v>-0.1405496486574055</v>
       </c>
       <c r="I37">
-        <v>-0.12697941297134699</v>
+        <v>-0.113401134929879</v>
       </c>
       <c r="J37">
-        <v>-5.3885868540855072E-2</v>
+        <v>-0.03948684780998863</v>
       </c>
       <c r="K37">
-        <v>0.19695623096068479</v>
+        <v>0.1933866813988108</v>
       </c>
       <c r="L37">
-        <v>0.24977802187413259</v>
+        <v>0.2554249321929242</v>
       </c>
       <c r="M37">
-        <v>0.27770330397521992</v>
+        <v>0.2835743438069128</v>
       </c>
       <c r="N37">
-        <v>0.26293628286427828</v>
+        <v>0.2687562925303149</v>
       </c>
       <c r="O37">
-        <v>0.24083998932570719</v>
+        <v>0.2426314972002794</v>
       </c>
       <c r="P37">
-        <v>0.22183916474795071</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.2276630150441347</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>-4.3801088320455352E-2</v>
+        <v>-0.03727552558757564</v>
       </c>
       <c r="C38">
-        <v>-0.14827591674105339</v>
+        <v>-0.1435262450151322</v>
       </c>
       <c r="D38">
-        <v>-0.16280587838318261</v>
+        <v>-0.1508318119824851</v>
       </c>
       <c r="E38">
-        <v>-0.1209550357620264</v>
+        <v>-0.1115593143174443</v>
       </c>
       <c r="F38">
-        <v>-0.1139160987618993</v>
+        <v>-0.105614920281805</v>
       </c>
       <c r="G38">
-        <v>-9.3569191508868166E-2</v>
+        <v>-0.08202826358775867</v>
       </c>
       <c r="H38">
-        <v>-0.14457914526915311</v>
+        <v>-0.1257921668587328</v>
       </c>
       <c r="I38">
-        <v>-0.1126334383432147</v>
+        <v>-0.1105558676181397</v>
       </c>
       <c r="J38">
-        <v>-3.9589363986853171E-2</v>
+        <v>-0.04090440103971053</v>
       </c>
       <c r="K38">
-        <v>0.19710738602934469</v>
+        <v>0.1986783197230448</v>
       </c>
       <c r="L38">
-        <v>0.25136618235049052</v>
+        <v>0.2541774640753492</v>
       </c>
       <c r="M38">
-        <v>0.28169179168102793</v>
+        <v>0.2767007878428994</v>
       </c>
       <c r="N38">
-        <v>0.27186972445167401</v>
+        <v>0.2773606710076459</v>
       </c>
       <c r="O38">
-        <v>0.25843208122455819</v>
+        <v>0.2629365165048381</v>
       </c>
       <c r="P38">
-        <v>0.24902662242886781</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.2517336270727608</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>-4.0766913067889612E-2</v>
+        <v>-0.04128336508082256</v>
       </c>
       <c r="C39">
-        <v>-0.14709592736646021</v>
+        <v>-0.1471700609462354</v>
       </c>
       <c r="D39">
-        <v>-0.16236451290131129</v>
+        <v>-0.1564479439541555</v>
       </c>
       <c r="E39">
-        <v>-0.1241177273403198</v>
+        <v>-0.1202866311097909</v>
       </c>
       <c r="F39">
-        <v>-0.11867030477898551</v>
+        <v>-0.1075374350977399</v>
       </c>
       <c r="G39">
-        <v>-9.5679999222852072E-2</v>
+        <v>-0.08773565509539887</v>
       </c>
       <c r="H39">
-        <v>-0.15681661265728869</v>
+        <v>-0.1543869191957263</v>
       </c>
       <c r="I39">
-        <v>-0.12575920017284661</v>
+        <v>-0.1179265276884757</v>
       </c>
       <c r="J39">
-        <v>-6.3696950516841891E-2</v>
+        <v>-0.04300467859468477</v>
       </c>
       <c r="K39">
-        <v>0.16734744956641259</v>
+        <v>0.1855910746512651</v>
       </c>
       <c r="L39">
-        <v>0.23909304542715359</v>
+        <v>0.2434047180952124</v>
       </c>
       <c r="M39">
-        <v>0.26491646632498811</v>
+        <v>0.269827517579205</v>
       </c>
       <c r="N39">
-        <v>0.26502633139983978</v>
+        <v>0.2674393984388367</v>
       </c>
       <c r="O39">
-        <v>0.2456047908708773</v>
+        <v>0.2486444965570284</v>
       </c>
       <c r="P39">
-        <v>0.24530885512436221</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.2413531395492658</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>-4.1501038663588299E-2</v>
+        <v>-0.04212224482690578</v>
       </c>
       <c r="C40">
-        <v>-0.1491719738359463</v>
+        <v>-0.1421068930745037</v>
       </c>
       <c r="D40">
-        <v>-0.1609445372900401</v>
+        <v>-0.1509030616635356</v>
       </c>
       <c r="E40">
-        <v>-0.1248252597581397</v>
+        <v>-0.1140250191409309</v>
       </c>
       <c r="F40">
-        <v>-0.1132283273291966</v>
+        <v>-0.1060251613437894</v>
       </c>
       <c r="G40">
-        <v>-8.8181171968347932E-2</v>
+        <v>-0.08727065022843601</v>
       </c>
       <c r="H40">
-        <v>-0.14045349067212909</v>
+        <v>-0.1376698124910503</v>
       </c>
       <c r="I40">
-        <v>-0.11097176141969819</v>
+        <v>-0.1195011704327201</v>
       </c>
       <c r="J40">
-        <v>-4.8994772831402987E-2</v>
+        <v>-0.0498602361834714</v>
       </c>
       <c r="K40">
-        <v>0.18673131811318139</v>
+        <v>0.1932400243766574</v>
       </c>
       <c r="L40">
-        <v>0.23909492495549281</v>
+        <v>0.2459475917095718</v>
       </c>
       <c r="M40">
-        <v>0.25892603818721499</v>
+        <v>0.2721054472782695</v>
       </c>
       <c r="N40">
-        <v>0.27737321503252532</v>
+        <v>0.2888374330416307</v>
       </c>
       <c r="O40">
-        <v>0.27633612381147499</v>
+        <v>0.282578705963172</v>
       </c>
       <c r="P40">
-        <v>0.29177638970318648</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.3046605728993425</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>-4.5381650504526118E-2</v>
+        <v>-0.04625197306646768</v>
       </c>
       <c r="C41">
-        <v>-0.18186284668439459</v>
+        <v>-0.1749644627007972</v>
       </c>
       <c r="D41">
-        <v>-0.1184084286667523</v>
+        <v>-0.1159657215022772</v>
       </c>
       <c r="E41">
-        <v>-7.7774192566559666E-2</v>
+        <v>-0.08429124641134955</v>
       </c>
       <c r="F41">
-        <v>-0.1030779253203899</v>
+        <v>-0.1028539411078629</v>
       </c>
       <c r="G41">
-        <v>-7.9853708157187439E-2</v>
+        <v>-0.08057460656627742</v>
       </c>
       <c r="H41">
-        <v>2.8326952802996661E-2</v>
+        <v>0.01695680006807039</v>
       </c>
       <c r="I41">
-        <v>5.2320014585931961E-2</v>
+        <v>0.04230504136508662</v>
       </c>
       <c r="J41">
-        <v>4.2657823016378632E-2</v>
+        <v>0.0413959035115388</v>
       </c>
       <c r="K41">
-        <v>6.5410845963221886E-2</v>
+        <v>0.07563392044366418</v>
       </c>
       <c r="L41">
-        <v>6.1393542898481618E-2</v>
+        <v>0.06653051531235009</v>
       </c>
       <c r="M41">
-        <v>1.5506151779793099E-2</v>
+        <v>0.02326725599285852</v>
       </c>
       <c r="N41">
-        <v>5.5662310697616381E-2</v>
+        <v>0.06421266239844411</v>
       </c>
       <c r="O41">
-        <v>8.2406576103709495E-2</v>
+        <v>0.09191835640753723</v>
       </c>
       <c r="P41">
-        <v>9.1767092869715433E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.102680594596799</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>-4.6575000550627528E-2</v>
+        <v>-0.04596243312360057</v>
       </c>
       <c r="C42">
-        <v>-0.16707816252113941</v>
+        <v>-0.1612410354045998</v>
       </c>
       <c r="D42">
-        <v>-0.14054786906137889</v>
+        <v>-0.1344329785429776</v>
       </c>
       <c r="E42">
-        <v>-4.4335728685332733E-2</v>
+        <v>-0.0335130711165406</v>
       </c>
       <c r="F42">
-        <v>2.4239989970769212E-2</v>
+        <v>0.03536844894231593</v>
       </c>
       <c r="G42">
-        <v>0.12735502668411389</v>
+        <v>0.1311091274996921</v>
       </c>
       <c r="H42">
-        <v>0.26870183978252993</v>
+        <v>0.2571426835624245</v>
       </c>
       <c r="I42">
-        <v>0.25089688681924471</v>
+        <v>0.2463051443400934</v>
       </c>
       <c r="J42">
-        <v>0.20391658136147081</v>
+        <v>0.1994795726531932</v>
       </c>
       <c r="K42">
-        <v>0.18088788856900759</v>
+        <v>0.1762284681830604</v>
       </c>
       <c r="L42">
-        <v>0.1863839622360848</v>
+        <v>0.1784867228662888</v>
       </c>
       <c r="M42">
-        <v>0.19400317248015209</v>
+        <v>0.1926409299885658</v>
       </c>
       <c r="N42">
-        <v>0.2451968774207402</v>
+        <v>0.2297963702942683</v>
       </c>
       <c r="O42">
-        <v>0.27254285511710169</v>
+        <v>0.2583333897506042</v>
       </c>
       <c r="P42">
-        <v>0.27605142105191799</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.264481407307693</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>-4.3345513648586027E-2</v>
+        <v>-0.04169357859158482</v>
       </c>
       <c r="C43">
-        <v>-0.15410311262924609</v>
+        <v>-0.1505566193668235</v>
       </c>
       <c r="D43">
-        <v>-0.1199797807935182</v>
+        <v>-0.1130696873612765</v>
       </c>
       <c r="E43">
-        <v>-1.6838498837149309E-2</v>
+        <v>-0.02515424914046004</v>
       </c>
       <c r="F43">
-        <v>1.2105573824875929E-2</v>
+        <v>0.01301548293774969</v>
       </c>
       <c r="G43">
-        <v>9.7170732808818355E-2</v>
+        <v>0.1037820848584118</v>
       </c>
       <c r="H43">
-        <v>0.22800895796921281</v>
+        <v>0.2271858911307</v>
       </c>
       <c r="I43">
-        <v>0.2357500576006307</v>
+        <v>0.239347971302835</v>
       </c>
       <c r="J43">
-        <v>0.24284114179705699</v>
+        <v>0.2367225765627253</v>
       </c>
       <c r="K43">
-        <v>0.24823873892938891</v>
+        <v>0.2433727949278686</v>
       </c>
       <c r="L43">
-        <v>0.24448395847666499</v>
+        <v>0.2406601396667453</v>
       </c>
       <c r="M43">
-        <v>0.28221959162444188</v>
+        <v>0.2740498581576624</v>
       </c>
       <c r="N43">
-        <v>0.29191414685278888</v>
+        <v>0.285143608792408</v>
       </c>
       <c r="O43">
-        <v>0.28965820927333619</v>
+        <v>0.2854242970635281</v>
       </c>
       <c r="P43">
-        <v>0.29295547876344402</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.2959337544908345</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>-6.8932643943027005E-2</v>
+        <v>-0.07583542535670965</v>
       </c>
       <c r="C44">
-        <v>-9.8880953531468599E-2</v>
+        <v>-0.09944650486294521</v>
       </c>
       <c r="D44">
-        <v>-5.8228315329460368E-3</v>
+        <v>0.001743146087469113</v>
       </c>
       <c r="E44">
-        <v>-4.2332256560574433E-2</v>
+        <v>-0.0435870779463847</v>
       </c>
       <c r="F44">
-        <v>7.2224592260309042E-2</v>
+        <v>0.07539836301484924</v>
       </c>
       <c r="G44">
-        <v>0.13118664840660599</v>
+        <v>0.1470714847740439</v>
       </c>
       <c r="H44">
-        <v>0.1008155141659374</v>
+        <v>0.1037977607503765</v>
       </c>
       <c r="I44">
-        <v>5.6497637378716707E-2</v>
+        <v>0.05355942527023202</v>
       </c>
       <c r="J44">
-        <v>7.2482509558813579E-2</v>
+        <v>0.0750627242907522</v>
       </c>
       <c r="K44">
-        <v>0.12728382508536529</v>
+        <v>0.1251382065341975</v>
       </c>
       <c r="L44">
-        <v>0.13734352097064001</v>
+        <v>0.1365677807121645</v>
       </c>
       <c r="M44">
-        <v>0.16525886502965331</v>
+        <v>0.1669129164245302</v>
       </c>
       <c r="N44">
-        <v>0.15578373983269031</v>
+        <v>0.1594435112584522</v>
       </c>
       <c r="O44">
-        <v>0.12513932991152399</v>
+        <v>0.1290582635680644</v>
       </c>
       <c r="P44">
-        <v>6.6261772786394404E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.07668652557900787</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>-5.1539056545613048E-2</v>
+        <v>-0.05441066455536687</v>
       </c>
       <c r="C45">
-        <v>-0.22553372606898181</v>
+        <v>-0.2287525949217221</v>
       </c>
       <c r="D45">
-        <v>-0.1486723427025928</v>
+        <v>-0.1474495371313247</v>
       </c>
       <c r="E45">
-        <v>-0.20196705946240451</v>
+        <v>-0.2033871772680559</v>
       </c>
       <c r="F45">
-        <v>-0.1237859576585537</v>
+        <v>-0.126866305081519</v>
       </c>
       <c r="G45">
-        <v>-0.12074679360705121</v>
+        <v>-0.1237991840678845</v>
       </c>
       <c r="H45">
-        <v>-6.9113751444013716E-2</v>
+        <v>-0.07606818451582199</v>
       </c>
       <c r="I45">
-        <v>6.9277145845227767E-4</v>
+        <v>-0.005116520260501784</v>
       </c>
       <c r="J45">
-        <v>-3.819506450756039E-2</v>
+        <v>-0.04354419321032169</v>
       </c>
       <c r="K45">
-        <v>-7.293972935462735E-2</v>
+        <v>-0.07567470564610476</v>
       </c>
       <c r="L45">
-        <v>-6.9062714161606614E-2</v>
+        <v>-0.06079747423056899</v>
       </c>
       <c r="M45">
-        <v>-9.4393206140363839E-2</v>
+        <v>-0.08604719696958087</v>
       </c>
       <c r="N45">
-        <v>-0.15108731752778901</v>
+        <v>-0.1404412517322246</v>
       </c>
       <c r="O45">
-        <v>-0.1512864871476923</v>
+        <v>-0.1399937231574614</v>
       </c>
       <c r="P45">
-        <v>-0.14860142357338221</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>-0.141500291957582</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>-1.6529503939454619E-2</v>
+        <v>-0.01770140893973659</v>
       </c>
       <c r="C46">
-        <v>-0.1001840436230635</v>
+        <v>-0.09528614336493811</v>
       </c>
       <c r="D46">
-        <v>-0.2065951292352847</v>
+        <v>-0.210684352537194</v>
       </c>
       <c r="E46">
-        <v>1.8558000352822838E-2</v>
+        <v>0.03511873931610918</v>
       </c>
       <c r="F46">
-        <v>0.13455292748189959</v>
+        <v>0.1445570172035717</v>
       </c>
       <c r="G46">
-        <v>0.18765033577792359</v>
+        <v>0.1816916749156593</v>
       </c>
       <c r="H46">
-        <v>0.30089005402241342</v>
+        <v>0.3105309711557367</v>
       </c>
       <c r="I46">
-        <v>0.30538298412995818</v>
+        <v>0.3134531691990743</v>
       </c>
       <c r="J46">
-        <v>0.29634852968637998</v>
+        <v>0.2960020835183754</v>
       </c>
       <c r="K46">
-        <v>0.34439034200455432</v>
+        <v>0.3442058253641982</v>
       </c>
       <c r="L46">
-        <v>0.35550551669679309</v>
+        <v>0.35201646767259</v>
       </c>
       <c r="M46">
-        <v>0.34235111732210333</v>
+        <v>0.3421132654813051</v>
       </c>
       <c r="N46">
-        <v>0.34131520734925408</v>
+        <v>0.3361414766036234</v>
       </c>
       <c r="O46">
-        <v>0.3348259057562154</v>
+        <v>0.3373238563197498</v>
       </c>
       <c r="P46">
-        <v>0.31940286130360651</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.3164625982388747</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>-2.7841436144541098E-2</v>
+        <v>-0.02728578359445202</v>
       </c>
       <c r="C47">
-        <v>-8.8866696135414522E-2</v>
+        <v>-0.09824768805077648</v>
       </c>
       <c r="D47">
-        <v>-5.9290190264350853E-2</v>
+        <v>-0.07834126284727824</v>
       </c>
       <c r="E47">
-        <v>5.185558421081974E-2</v>
+        <v>0.04054849817349221</v>
       </c>
       <c r="F47">
-        <v>0.1875612775986206</v>
+        <v>0.1851671824408168</v>
       </c>
       <c r="G47">
-        <v>0.21591625529606989</v>
+        <v>0.2101987838532292</v>
       </c>
       <c r="H47">
-        <v>0.26771570606726047</v>
+        <v>0.2677919762366169</v>
       </c>
       <c r="I47">
-        <v>0.27894048123987242</v>
+        <v>0.279588053059001</v>
       </c>
       <c r="J47">
-        <v>0.25178359481828039</v>
+        <v>0.2492805504150287</v>
       </c>
       <c r="K47">
-        <v>0.27248159950470141</v>
+        <v>0.2699624619436021</v>
       </c>
       <c r="L47">
-        <v>0.28572609023474971</v>
+        <v>0.2838699966840019</v>
       </c>
       <c r="M47">
-        <v>0.27916938326438412</v>
+        <v>0.2771843004671938</v>
       </c>
       <c r="N47">
-        <v>0.24876615294658411</v>
+        <v>0.2457349425050634</v>
       </c>
       <c r="O47">
-        <v>0.21650638163440031</v>
+        <v>0.2197119109064018</v>
       </c>
       <c r="P47">
-        <v>0.19516991065935629</v>
+        <v>0.1922180030125828</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P19 B21:P47 B20:M20 O20:P20">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_ADJR2.xlsx
@@ -1,21 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV0_ADJR2</t>
+  </si>
+  <si>
+    <t>LV1_ADJR2</t>
+  </si>
+  <si>
+    <t>LV2_ADJR2</t>
+  </si>
+  <si>
+    <t>LV3_ADJR2</t>
+  </si>
+  <si>
+    <t>LV4_ADJR2</t>
+  </si>
+  <si>
+    <t>LV5_ADJR2</t>
+  </si>
+  <si>
+    <t>LV6_ADJR2</t>
+  </si>
+  <si>
+    <t>LV7_ADJR2</t>
+  </si>
+  <si>
+    <t>LV8_ADJR2</t>
+  </si>
+  <si>
+    <t>LV9_ADJR2</t>
+  </si>
+  <si>
+    <t>LV10_ADJR2</t>
+  </si>
+  <si>
+    <t>LV11_ADJR2</t>
+  </si>
+  <si>
+    <t>LV12_ADJR2</t>
+  </si>
+  <si>
+    <t>LV13_ADJR2</t>
+  </si>
+  <si>
+    <t>LV14_ADJR2</t>
+  </si>
+  <si>
+    <t>LV15_ADJR2</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -40,7 +227,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,26 +235,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +320,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +352,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +387,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2485 +563,2306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_ADJR2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_ADJR2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_ADJR2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_ADJR2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_ADJR2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_ADJR2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_ADJR2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_ADJR2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_ADJR2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_ADJR2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_ADJR2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_ADJR2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_ADJR2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_ADJR2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_ADJR2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>-0.0309091624346408</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C2">
-        <v>-0.05257945569618049</v>
+        <v>-3.4797002392697153E-2</v>
       </c>
       <c r="D2">
-        <v>-0.05908733374849533</v>
+        <v>-5.3852362548961433E-2</v>
       </c>
       <c r="E2">
-        <v>-0.06221966240973618</v>
+        <v>-5.9897405745343912E-2</v>
       </c>
       <c r="F2">
-        <v>-0.05621151993175835</v>
+        <v>-6.1285748729154002E-2</v>
       </c>
       <c r="G2">
-        <v>-0.06652286286126899</v>
+        <v>-6.0727227790227677E-2</v>
       </c>
       <c r="H2">
-        <v>-0.005236771100586484</v>
+        <v>-6.2178301385081472E-2</v>
       </c>
       <c r="I2">
-        <v>0.08428563584582191</v>
+        <v>3.2733503322159231E-3</v>
       </c>
       <c r="J2">
-        <v>0.04694856235413453</v>
+        <v>9.2123928561410856E-2</v>
       </c>
       <c r="K2">
-        <v>0.0822075714738514</v>
+        <v>4.8668925423998109E-2</v>
       </c>
       <c r="L2">
-        <v>0.1798434835851796</v>
+        <v>9.7722210924029565E-2</v>
       </c>
       <c r="M2">
-        <v>0.213295625583303</v>
+        <v>0.1849994568601051</v>
       </c>
       <c r="N2">
-        <v>0.3006234988040885</v>
+        <v>0.2213144588893225</v>
       </c>
       <c r="O2">
-        <v>0.3778582454072691</v>
-      </c>
-      <c r="P2">
-        <v>0.4239042078922813</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.3042350444268288</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.38351382896663039</v>
+      </c>
+      <c r="Q2">
+        <v>0.42237281923662878</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>-0.02099456057005921</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C3">
-        <v>-0.04628140601128741</v>
+        <v>-2.297019530262016E-2</v>
       </c>
       <c r="D3">
-        <v>-0.1715025286902799</v>
+        <v>-4.5968467411213298E-2</v>
       </c>
       <c r="E3">
-        <v>0.0222596911735379</v>
+        <v>-0.17678579464570121</v>
       </c>
       <c r="F3">
-        <v>0.1215331771838012</v>
+        <v>1.327218200258222E-2</v>
       </c>
       <c r="G3">
-        <v>0.1742301648650524</v>
+        <v>0.10109382899849589</v>
       </c>
       <c r="H3">
-        <v>0.2175184304848574</v>
+        <v>0.17035300497168901</v>
       </c>
       <c r="I3">
-        <v>0.2344787249557625</v>
+        <v>0.22259255523281901</v>
       </c>
       <c r="J3">
-        <v>0.2981525886886429</v>
-      </c>
-      <c r="K3">
-        <v>0.3414081779645546</v>
+        <v>0.23866441819276701</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.30015143523084759</v>
       </c>
       <c r="L3">
-        <v>0.3403000110217872</v>
+        <v>0.34401284560681411</v>
       </c>
       <c r="M3">
-        <v>0.3452628011114079</v>
+        <v>0.34039027330502369</v>
       </c>
       <c r="N3">
-        <v>0.3191178717462257</v>
+        <v>0.34642699295282792</v>
       </c>
       <c r="O3">
-        <v>0.3196921508602512</v>
+        <v>0.31375452773715001</v>
       </c>
       <c r="P3">
-        <v>0.3449017399220294</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.30866869115975087</v>
+      </c>
+      <c r="Q3">
+        <v>0.3385053742875852</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>-0.03391041880822396</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C4">
-        <v>-0.04450085330911528</v>
+        <v>-3.0529963701704431E-2</v>
       </c>
       <c r="D4">
-        <v>-0.1218205332258667</v>
+        <v>-4.633740859492419E-2</v>
       </c>
       <c r="E4">
-        <v>-0.1151296686492731</v>
+        <v>-0.13210348132686009</v>
       </c>
       <c r="F4">
-        <v>-0.1753046999165144</v>
+        <v>-0.13446472951722441</v>
       </c>
       <c r="G4">
-        <v>-0.0407882078006774</v>
+        <v>-0.20493173416039301</v>
       </c>
       <c r="H4">
-        <v>0.09876404245641386</v>
+        <v>-6.1143796807262507E-2</v>
       </c>
       <c r="I4">
-        <v>0.115756660081455</v>
+        <v>8.9102429296634783E-2</v>
       </c>
       <c r="J4">
-        <v>0.138888833608373</v>
+        <v>0.1124041020806935</v>
       </c>
       <c r="K4">
-        <v>0.1982275277741247</v>
+        <v>0.12817378062137019</v>
       </c>
       <c r="L4">
-        <v>0.273705796310258</v>
+        <v>0.2045379271530105</v>
       </c>
       <c r="M4">
-        <v>0.3342140765688415</v>
-      </c>
-      <c r="N4">
-        <v>0.3774335296200462</v>
+        <v>0.27391927099005747</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.33352378803126748</v>
       </c>
       <c r="O4">
-        <v>0.3836894878116494</v>
+        <v>0.37164408117120118</v>
       </c>
       <c r="P4">
-        <v>0.3800945285883095</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.38461116074320839</v>
+      </c>
+      <c r="Q4">
+        <v>0.377970184491979</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>-0.02258972649150686</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C5">
-        <v>-0.07406892567203299</v>
+        <v>-2.5592421513200379E-2</v>
       </c>
       <c r="D5">
-        <v>-0.07546516132249291</v>
+        <v>-7.5823678327988614E-2</v>
       </c>
       <c r="E5">
-        <v>-0.1287928969767078</v>
+        <v>-8.6703235843808721E-2</v>
       </c>
       <c r="F5">
-        <v>0.0883167245715652</v>
+        <v>-0.13410967754853961</v>
       </c>
       <c r="G5">
-        <v>0.1939927682533635</v>
+        <v>8.5679900056743544E-2</v>
       </c>
       <c r="H5">
-        <v>0.2389730620112396</v>
+        <v>0.18077210974006719</v>
       </c>
       <c r="I5">
-        <v>0.30175240713644</v>
+        <v>0.2322684848636255</v>
       </c>
       <c r="J5">
-        <v>0.3679258907915758</v>
-      </c>
-      <c r="K5">
-        <v>0.3985223993618913</v>
+        <v>0.29811458586599782</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.37031066127109269</v>
       </c>
       <c r="L5">
-        <v>0.4344029400185744</v>
+        <v>0.40789063508637707</v>
       </c>
       <c r="M5">
-        <v>0.432770679606483</v>
+        <v>0.44791958086994171</v>
       </c>
       <c r="N5">
-        <v>0.4103732998420652</v>
+        <v>0.44721981160569529</v>
       </c>
       <c r="O5">
-        <v>0.3900654837708717</v>
+        <v>0.42620211586171591</v>
       </c>
       <c r="P5">
-        <v>0.3687432758577957</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.40199667259052241</v>
+      </c>
+      <c r="Q5">
+        <v>0.37961432208467799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>-0.02470151514924269</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C6">
-        <v>-0.07422163510650634</v>
+        <v>-2.5850253404275259E-2</v>
       </c>
       <c r="D6">
-        <v>-0.06632916095550452</v>
+        <v>-7.6382791013304432E-2</v>
       </c>
       <c r="E6">
-        <v>-0.05622015346963644</v>
+        <v>-8.6185639666446878E-2</v>
       </c>
       <c r="F6">
-        <v>0.1604677238239528</v>
+        <v>-6.9191177121966416E-2</v>
       </c>
       <c r="G6">
-        <v>0.2928380113995377</v>
+        <v>0.16709037260646131</v>
       </c>
       <c r="H6">
-        <v>0.3378272338052366</v>
+        <v>0.28760506680778042</v>
       </c>
       <c r="I6">
-        <v>0.4062027103969788</v>
-      </c>
-      <c r="J6">
-        <v>0.4475410389668669</v>
+        <v>0.33725096249828468</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.40921813673547358</v>
       </c>
       <c r="K6">
-        <v>0.4711427612549062</v>
+        <v>0.45395614605220791</v>
       </c>
       <c r="L6">
-        <v>0.4885384199565682</v>
+        <v>0.47327413088068482</v>
       </c>
       <c r="M6">
-        <v>0.492700514931418</v>
+        <v>0.49241507238240562</v>
       </c>
       <c r="N6">
-        <v>0.4865439492426533</v>
+        <v>0.49869984312262078</v>
       </c>
       <c r="O6">
-        <v>0.4923924714048941</v>
+        <v>0.49061169270194049</v>
       </c>
       <c r="P6">
-        <v>0.4804443180964985</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.49498387994264659</v>
+      </c>
+      <c r="Q6">
+        <v>0.47808860452312268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>-0.03749815348691349</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C7">
-        <v>-0.05314375114110289</v>
+        <v>-3.5313416952168407E-2</v>
       </c>
       <c r="D7">
-        <v>-0.1431042207696032</v>
+        <v>-5.0760234490325358E-2</v>
       </c>
       <c r="E7">
-        <v>-0.1514386261633123</v>
+        <v>-0.13980099710194779</v>
       </c>
       <c r="F7">
-        <v>-0.1983417758320659</v>
+        <v>-0.15229786172990081</v>
       </c>
       <c r="G7">
-        <v>-0.1858145751046568</v>
+        <v>-0.19872465324562799</v>
       </c>
       <c r="H7">
-        <v>-0.02690196213905235</v>
+        <v>-0.1975640377042476</v>
       </c>
       <c r="I7">
-        <v>0.09514373636594353</v>
+        <v>-3.7333180360937239E-2</v>
       </c>
       <c r="J7">
-        <v>0.09517416303117668</v>
+        <v>8.5229553613779374E-2</v>
       </c>
       <c r="K7">
-        <v>0.1348576175260295</v>
+        <v>8.4434355404679126E-2</v>
       </c>
       <c r="L7">
-        <v>0.2213037919388069</v>
+        <v>0.1343547276286095</v>
       </c>
       <c r="M7">
-        <v>0.2941299475923215</v>
+        <v>0.2210376551103917</v>
       </c>
       <c r="N7">
-        <v>0.3466617927572416</v>
+        <v>0.29618177589191702</v>
       </c>
       <c r="O7">
-        <v>0.3788309949068405</v>
+        <v>0.35418515249969318</v>
       </c>
       <c r="P7">
-        <v>0.3940881191588784</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.38851983610111662</v>
+      </c>
+      <c r="Q7">
+        <v>0.40344506769835708</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>-0.02822205152125482</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C8">
-        <v>-0.04192576910322471</v>
+        <v>-3.0673373728049659E-2</v>
       </c>
       <c r="D8">
-        <v>-0.1174881784458682</v>
+        <v>-4.5154341286073638E-2</v>
       </c>
       <c r="E8">
-        <v>-0.1515404145752722</v>
+        <v>-0.12013862621396559</v>
       </c>
       <c r="F8">
-        <v>-0.08011892868121069</v>
+        <v>-0.14570452630148709</v>
       </c>
       <c r="G8">
-        <v>0.0145942061382597</v>
+        <v>-8.8832582090157319E-2</v>
       </c>
       <c r="H8">
-        <v>0.07490112348261307</v>
+        <v>5.0141516426768758E-3</v>
       </c>
       <c r="I8">
-        <v>0.1678207901555316</v>
+        <v>6.1920897621795049E-2</v>
       </c>
       <c r="J8">
-        <v>0.2145275439454228</v>
+        <v>0.15520919564922339</v>
       </c>
       <c r="K8">
-        <v>0.3291252189387641</v>
+        <v>0.19761458331770529</v>
       </c>
       <c r="L8">
-        <v>0.3430413637435711</v>
+        <v>0.31732831697652147</v>
       </c>
       <c r="M8">
-        <v>0.3871785968134269</v>
+        <v>0.31967382676367501</v>
       </c>
       <c r="N8">
-        <v>0.4252945403284348</v>
+        <v>0.36861382987531249</v>
       </c>
       <c r="O8">
-        <v>0.4288182271323899</v>
+        <v>0.40761368752620752</v>
       </c>
       <c r="P8">
-        <v>0.4192264052849704</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.40652458139807202</v>
+      </c>
+      <c r="Q8">
+        <v>0.40178598509664459</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>-0.02500673426692134</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C9">
-        <v>-0.03831791356756908</v>
+        <v>-2.8356694345300741E-2</v>
       </c>
       <c r="D9">
-        <v>-0.1115692124485748</v>
+        <v>-4.4029789519784583E-2</v>
       </c>
       <c r="E9">
-        <v>-0.1296625334604877</v>
+        <v>-0.1113572878225689</v>
       </c>
       <c r="F9">
-        <v>-0.0778477268618899</v>
+        <v>-0.1386696164190733</v>
       </c>
       <c r="G9">
-        <v>0.02009080281697788</v>
+        <v>-8.0016407876304485E-2</v>
       </c>
       <c r="H9">
-        <v>0.07836097220370336</v>
+        <v>1.211071514087647E-2</v>
       </c>
       <c r="I9">
-        <v>0.1721654299079403</v>
+        <v>6.3673143171865773E-2</v>
       </c>
       <c r="J9">
-        <v>0.2116863637300102</v>
+        <v>0.15571799775814199</v>
       </c>
       <c r="K9">
-        <v>0.3644158392406011</v>
+        <v>0.19852559876529699</v>
       </c>
       <c r="L9">
-        <v>0.3800440761716107</v>
+        <v>0.36400121847479838</v>
       </c>
       <c r="M9">
-        <v>0.4157792172097211</v>
+        <v>0.37195380508948789</v>
       </c>
       <c r="N9">
-        <v>0.4481802000175921</v>
+        <v>0.40838180321310169</v>
       </c>
       <c r="O9">
-        <v>0.4543067844441068</v>
+        <v>0.44323109846547692</v>
       </c>
       <c r="P9">
-        <v>0.457719294988321</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.45380873073644901</v>
+      </c>
+      <c r="Q9">
+        <v>0.45459008525786571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>-0.02866336127349795</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C10">
-        <v>-0.04460708164022938</v>
+        <v>-2.6691510416025459E-2</v>
       </c>
       <c r="D10">
-        <v>-0.1150810561837532</v>
+        <v>-4.1858118338935532E-2</v>
       </c>
       <c r="E10">
-        <v>-0.1319697298468274</v>
+        <v>-0.1202150650534201</v>
       </c>
       <c r="F10">
-        <v>-0.0753724711151416</v>
+        <v>-0.14060563264021159</v>
       </c>
       <c r="G10">
-        <v>0.006360993082261651</v>
+        <v>-8.8858877643691797E-2</v>
       </c>
       <c r="H10">
-        <v>0.06310864494525159</v>
+        <v>4.061695245481692E-3</v>
       </c>
       <c r="I10">
-        <v>0.1624453984276476</v>
+        <v>6.2055296756127233E-2</v>
       </c>
       <c r="J10">
-        <v>0.2021957335534782</v>
+        <v>0.153900068892805</v>
       </c>
       <c r="K10">
-        <v>0.3566734188903294</v>
+        <v>0.19003576239502121</v>
       </c>
       <c r="L10">
-        <v>0.3584204150407703</v>
+        <v>0.35082957137821158</v>
       </c>
       <c r="M10">
-        <v>0.3991362255591526</v>
+        <v>0.35496222479345929</v>
       </c>
       <c r="N10">
-        <v>0.4362774875411413</v>
+        <v>0.3917028893041955</v>
       </c>
       <c r="O10">
-        <v>0.4388062275915379</v>
+        <v>0.42227299535301099</v>
       </c>
       <c r="P10">
-        <v>0.4454525475829365</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.43369366094920292</v>
+      </c>
+      <c r="Q10">
+        <v>0.43841669395064897</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>-0.02769718729806322</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C11">
-        <v>-0.04402667613135063</v>
+        <v>-3.1722724002114053E-2</v>
       </c>
       <c r="D11">
-        <v>-0.1218938133269042</v>
+        <v>-4.8243464234574977E-2</v>
       </c>
       <c r="E11">
-        <v>-0.1503995583198461</v>
+        <v>-0.11861049016000159</v>
       </c>
       <c r="F11">
-        <v>-0.09663727050431177</v>
+        <v>-0.14389686322462991</v>
       </c>
       <c r="G11">
-        <v>0.01338133318182724</v>
+        <v>-8.6595925314043143E-2</v>
       </c>
       <c r="H11">
-        <v>0.05545259307247374</v>
+        <v>1.544607639932838E-3</v>
       </c>
       <c r="I11">
-        <v>0.1620163558978336</v>
+        <v>5.2442021193440748E-2</v>
       </c>
       <c r="J11">
-        <v>0.2044144097546948</v>
+        <v>0.15932834764442569</v>
       </c>
       <c r="K11">
-        <v>0.3640778577246913</v>
+        <v>0.19951507232676691</v>
       </c>
       <c r="L11">
-        <v>0.3764665590004471</v>
+        <v>0.36551557385989808</v>
       </c>
       <c r="M11">
-        <v>0.4169423823363976</v>
+        <v>0.37553916005814209</v>
       </c>
       <c r="N11">
-        <v>0.4472034738357168</v>
+        <v>0.41103313543729492</v>
       </c>
       <c r="O11">
-        <v>0.4476922196627712</v>
+        <v>0.44224312108231528</v>
       </c>
       <c r="P11">
-        <v>0.4523534541194133</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.4454911941956563</v>
+      </c>
+      <c r="Q11">
+        <v>0.44922050570578442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>-0.02201577025580785</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C12">
-        <v>-0.07430673468088028</v>
+        <v>-2.6756720230699811E-2</v>
       </c>
       <c r="D12">
-        <v>-0.07561349098209226</v>
+        <v>-8.262445416798482E-2</v>
       </c>
       <c r="E12">
-        <v>-0.130940944733508</v>
+        <v>-6.0555781754641248E-2</v>
       </c>
       <c r="F12">
-        <v>0.064408128350053</v>
+        <v>-0.1126078056758581</v>
       </c>
       <c r="G12">
-        <v>0.1450106228145099</v>
+        <v>8.3038805885201808E-2</v>
       </c>
       <c r="H12">
-        <v>0.26331349131969</v>
+        <v>0.1619302490917523</v>
       </c>
       <c r="I12">
-        <v>0.3631838351645765</v>
+        <v>0.26282856067089871</v>
       </c>
       <c r="J12">
-        <v>0.4103785254220804</v>
-      </c>
-      <c r="K12">
-        <v>0.439958352367881</v>
+        <v>0.3562546814911533</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.4022152290171252</v>
       </c>
       <c r="L12">
-        <v>0.4759218647209774</v>
+        <v>0.4291391883754393</v>
       </c>
       <c r="M12">
-        <v>0.4762214194306429</v>
+        <v>0.46742864352927838</v>
       </c>
       <c r="N12">
-        <v>0.4620176759196096</v>
+        <v>0.4703000350486054</v>
       </c>
       <c r="O12">
-        <v>0.4399373519631894</v>
+        <v>0.45601466572009841</v>
       </c>
       <c r="P12">
-        <v>0.4022700692030778</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.43238126119911929</v>
+      </c>
+      <c r="Q12">
+        <v>0.39357848338742141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>-0.02871481678430841</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C13">
-        <v>-0.1191047761086555</v>
+        <v>-2.3893721743971318E-2</v>
       </c>
       <c r="D13">
-        <v>-0.1166269199804432</v>
+        <v>-0.1201995310818109</v>
       </c>
       <c r="E13">
-        <v>-0.1347167804529344</v>
+        <v>-0.11278582961699091</v>
       </c>
       <c r="F13">
-        <v>-0.1673219192530294</v>
+        <v>-0.1307710511099584</v>
       </c>
       <c r="G13">
-        <v>-0.01120796853540059</v>
+        <v>-0.16347516271622001</v>
       </c>
       <c r="H13">
-        <v>0.01133049971278768</v>
+        <v>-2.0014291255418079E-2</v>
       </c>
       <c r="I13">
-        <v>0.07601770138459801</v>
+        <v>4.5532055195594617E-3</v>
       </c>
       <c r="J13">
-        <v>0.1548716441626851</v>
+        <v>6.9493762777614793E-2</v>
       </c>
       <c r="K13">
-        <v>0.2371361715672821</v>
+        <v>0.1507475264948315</v>
       </c>
       <c r="L13">
-        <v>0.2462393433134994</v>
+        <v>0.2255624104650143</v>
       </c>
       <c r="M13">
-        <v>0.2651524645387868</v>
+        <v>0.2468114642571993</v>
       </c>
       <c r="N13">
-        <v>0.2730555803998256</v>
+        <v>0.27164830868655371</v>
       </c>
       <c r="O13">
-        <v>0.284548687721848</v>
+        <v>0.27999002813846402</v>
       </c>
       <c r="P13">
-        <v>0.26531516354822</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.29211798403815659</v>
+      </c>
+      <c r="Q13">
+        <v>0.27158588194184802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>-0.033014167298918</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C14">
-        <v>-0.04942454943857603</v>
+        <v>-3.2056823448559507E-2</v>
       </c>
       <c r="D14">
-        <v>-0.1338161651621993</v>
+        <v>-4.9977206476293293E-2</v>
       </c>
       <c r="E14">
-        <v>-0.1412826055214594</v>
+        <v>-0.13529196978565361</v>
       </c>
       <c r="F14">
-        <v>-0.1934404049802867</v>
+        <v>-0.13787255983699709</v>
       </c>
       <c r="G14">
-        <v>-0.1772380632462671</v>
+        <v>-0.1823612950722413</v>
       </c>
       <c r="H14">
-        <v>-0.02936526123694279</v>
+        <v>-0.17215583078290531</v>
       </c>
       <c r="I14">
-        <v>0.08672961018097135</v>
+        <v>-2.6109325064025461E-2</v>
       </c>
       <c r="J14">
-        <v>0.08864325871547787</v>
+        <v>9.5030643239301923E-2</v>
       </c>
       <c r="K14">
-        <v>0.13243454096521</v>
+        <v>9.8049628573444791E-2</v>
       </c>
       <c r="L14">
-        <v>0.2395856993512682</v>
+        <v>0.13550138432443859</v>
       </c>
       <c r="M14">
-        <v>0.3512221473951909</v>
+        <v>0.2422404537912515</v>
       </c>
       <c r="N14">
-        <v>0.3900644987626132</v>
+        <v>0.35216079953019808</v>
       </c>
       <c r="O14">
-        <v>0.4213813440528286</v>
+        <v>0.39231027238477828</v>
       </c>
       <c r="P14">
-        <v>0.4441903823316233</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.42180983474555628</v>
+      </c>
+      <c r="Q14">
+        <v>0.43752674323861679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>-0.03688019357737708</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C15">
-        <v>-0.05448857940665732</v>
+        <v>-3.225698793633059E-2</v>
       </c>
       <c r="D15">
-        <v>-0.1394815988172089</v>
+        <v>-4.6693587386558801E-2</v>
       </c>
       <c r="E15">
-        <v>-0.1437385967901639</v>
+        <v>-0.13015989213235801</v>
       </c>
       <c r="F15">
-        <v>-0.196567633189575</v>
+        <v>-0.13403521419605441</v>
       </c>
       <c r="G15">
-        <v>-0.1905324388589958</v>
+        <v>-0.1732111876770267</v>
       </c>
       <c r="H15">
-        <v>-0.03789493614196134</v>
+        <v>-0.16227235910349719</v>
       </c>
       <c r="I15">
-        <v>0.07772779884847242</v>
+        <v>-2.4050872997839721E-2</v>
       </c>
       <c r="J15">
-        <v>0.06626625802485696</v>
+        <v>8.5267156938324179E-2</v>
       </c>
       <c r="K15">
-        <v>0.1247973312083399</v>
+        <v>9.0133774746307502E-2</v>
       </c>
       <c r="L15">
-        <v>0.22869462668166</v>
+        <v>0.13606005254448769</v>
       </c>
       <c r="M15">
-        <v>0.3387334917315651</v>
+        <v>0.22774902540564099</v>
       </c>
       <c r="N15">
-        <v>0.3793227573013357</v>
+        <v>0.33288180857280258</v>
       </c>
       <c r="O15">
-        <v>0.4081491467212865</v>
+        <v>0.37670493129914279</v>
       </c>
       <c r="P15">
-        <v>0.4327442998264037</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.41065195524308212</v>
+      </c>
+      <c r="Q15">
+        <v>0.42595766734959561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>-0.03385294351654881</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C16">
-        <v>-0.04751665261167776</v>
+        <v>-3.2128254400017313E-2</v>
       </c>
       <c r="D16">
-        <v>-0.1298814709306268</v>
+        <v>-4.8908083025720937E-2</v>
       </c>
       <c r="E16">
-        <v>-0.136262108252859</v>
+        <v>-0.1321495142724545</v>
       </c>
       <c r="F16">
-        <v>-0.1755901434039001</v>
+        <v>-0.1337959486829032</v>
       </c>
       <c r="G16">
-        <v>-0.1727221148170787</v>
+        <v>-0.18120708749362011</v>
       </c>
       <c r="H16">
-        <v>-0.03341884494458229</v>
+        <v>-0.16770387003464651</v>
       </c>
       <c r="I16">
-        <v>0.08641772015822323</v>
+        <v>-3.1240654157292189E-2</v>
       </c>
       <c r="J16">
-        <v>0.08668707066648144</v>
+        <v>8.9292872701355261E-2</v>
       </c>
       <c r="K16">
-        <v>0.1337698633383409</v>
+        <v>9.4522768796737031E-2</v>
       </c>
       <c r="L16">
-        <v>0.2314372544802493</v>
+        <v>0.13456358580573041</v>
       </c>
       <c r="M16">
-        <v>0.3465524716213722</v>
+        <v>0.23600575450099401</v>
       </c>
       <c r="N16">
-        <v>0.393852363926615</v>
+        <v>0.34486514936099449</v>
       </c>
       <c r="O16">
-        <v>0.4282383902507738</v>
+        <v>0.39440695270654458</v>
       </c>
       <c r="P16">
-        <v>0.444288408115127</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.42527071049439708</v>
+      </c>
+      <c r="Q16">
+        <v>0.4452644167506441</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>-0.03056041754341425</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C17">
-        <v>-0.04983270458941524</v>
+        <v>-3.6582284980212987E-2</v>
       </c>
       <c r="D17">
-        <v>-0.136308512687793</v>
+        <v>-5.4604092799943778E-2</v>
       </c>
       <c r="E17">
-        <v>-0.138386091441607</v>
+        <v>-0.14067261097012351</v>
       </c>
       <c r="F17">
-        <v>-0.1759887451036491</v>
+        <v>-0.14818844686370131</v>
       </c>
       <c r="G17">
-        <v>-0.1735594837073961</v>
+        <v>-0.18841560550341641</v>
       </c>
       <c r="H17">
-        <v>-0.03067260174656454</v>
+        <v>-0.17632276146798709</v>
       </c>
       <c r="I17">
-        <v>0.07741805991573414</v>
+        <v>-3.9508510390010763E-2</v>
       </c>
       <c r="J17">
-        <v>0.07107962836468631</v>
+        <v>6.9147618572639763E-2</v>
       </c>
       <c r="K17">
-        <v>0.1156275395874102</v>
+        <v>6.6385006526099896E-2</v>
       </c>
       <c r="L17">
-        <v>0.2013818318796746</v>
+        <v>0.1060623907290846</v>
       </c>
       <c r="M17">
-        <v>0.3101255585905598</v>
+        <v>0.19431045832193919</v>
       </c>
       <c r="N17">
-        <v>0.3502054877422179</v>
+        <v>0.30452947036026062</v>
       </c>
       <c r="O17">
-        <v>0.390271547401998</v>
+        <v>0.35009075511671639</v>
       </c>
       <c r="P17">
-        <v>0.4145873933533699</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.39194918376549698</v>
+      </c>
+      <c r="Q17">
+        <v>0.41770542632850249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>-0.0226674083076379</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C18">
-        <v>-0.07632034796402629</v>
+        <v>-2.3756067543613899E-2</v>
       </c>
       <c r="D18">
-        <v>-0.08097014696231396</v>
+        <v>-7.9058614168611069E-2</v>
       </c>
       <c r="E18">
-        <v>-0.1391488661092355</v>
+        <v>-8.751958323863368E-2</v>
       </c>
       <c r="F18">
-        <v>0.08529751765163408</v>
+        <v>-0.13553694558072621</v>
       </c>
       <c r="G18">
-        <v>0.1949474115686936</v>
+        <v>7.1183916496469157E-2</v>
       </c>
       <c r="H18">
-        <v>0.2555628148670935</v>
+        <v>0.19076535009557491</v>
       </c>
       <c r="I18">
-        <v>0.3517801075411581</v>
-      </c>
-      <c r="J18">
-        <v>0.4088598842132198</v>
+        <v>0.25243138480867322</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.34059576714046053</v>
       </c>
       <c r="K18">
-        <v>0.4275777662582173</v>
+        <v>0.40652708777689323</v>
       </c>
       <c r="L18">
-        <v>0.4586363551542268</v>
+        <v>0.42502916598843782</v>
       </c>
       <c r="M18">
-        <v>0.4648382889697032</v>
+        <v>0.46147604249632479</v>
       </c>
       <c r="N18">
-        <v>0.4381102729209496</v>
+        <v>0.46247980665436988</v>
       </c>
       <c r="O18">
-        <v>0.4127911731198863</v>
+        <v>0.43908841232743651</v>
       </c>
       <c r="P18">
-        <v>0.3956724611265258</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.4075689214923624</v>
+      </c>
+      <c r="Q18">
+        <v>0.39362028961660672</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>-0.0248550799648685</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C19">
-        <v>-0.08162533638583823</v>
+        <v>-2.4090244565841381E-2</v>
       </c>
       <c r="D19">
-        <v>-0.08904660885249449</v>
+        <v>-7.789115949750848E-2</v>
       </c>
       <c r="E19">
-        <v>-0.09584444319337346</v>
+        <v>-9.4758592183586718E-2</v>
       </c>
       <c r="F19">
-        <v>0.1427433825709921</v>
+        <v>-0.1012625582487755</v>
       </c>
       <c r="G19">
-        <v>0.2667403159834129</v>
+        <v>0.13165676007514179</v>
       </c>
       <c r="H19">
-        <v>0.3192126083969888</v>
+        <v>0.26538264307438802</v>
       </c>
       <c r="I19">
-        <v>0.3957326861958314</v>
-      </c>
-      <c r="J19">
-        <v>0.4420997467347939</v>
+        <v>0.31070789785609337</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.39158802694322642</v>
       </c>
       <c r="K19">
-        <v>0.4625459782102323</v>
+        <v>0.43945448334210219</v>
       </c>
       <c r="L19">
-        <v>0.4823262541897742</v>
+        <v>0.45572669705598551</v>
       </c>
       <c r="M19">
-        <v>0.4868281693384465</v>
+        <v>0.47783706620163352</v>
       </c>
       <c r="N19">
-        <v>0.4810826852982877</v>
+        <v>0.48026471719822911</v>
       </c>
       <c r="O19">
-        <v>0.4853215110979693</v>
+        <v>0.47329560430145767</v>
       </c>
       <c r="P19">
-        <v>0.479059385546237</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.48050467460297408</v>
+      </c>
+      <c r="Q19">
+        <v>0.47438743650092141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>-0.02366993559661576</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C20">
-        <v>-0.05289006852313399</v>
+        <v>-2.5210624954087012E-2</v>
       </c>
       <c r="D20">
-        <v>-0.08929995238558594</v>
+        <v>-6.7202189948162031E-2</v>
       </c>
       <c r="E20">
-        <v>0.007922172863827437</v>
+        <v>-8.5168737124641972E-2</v>
       </c>
       <c r="F20">
-        <v>0.1692404474038029</v>
+        <v>1.0385040688713411E-2</v>
       </c>
       <c r="G20">
-        <v>0.1980345152958766</v>
+        <v>0.16671312223890239</v>
       </c>
       <c r="H20">
-        <v>0.2979442829870516</v>
+        <v>0.2014136265641584</v>
       </c>
       <c r="I20">
-        <v>0.3738467579066261</v>
+        <v>0.30899183481191</v>
       </c>
       <c r="J20">
-        <v>0.41223128393061</v>
-      </c>
-      <c r="K20">
-        <v>0.4585111233697267</v>
+        <v>0.38139676541062623</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.41370969945143138</v>
       </c>
       <c r="L20">
-        <v>0.4771942045376036</v>
+        <v>0.46870492804754349</v>
       </c>
       <c r="M20">
-        <v>0.463953960320541</v>
+        <v>0.48583833243855751</v>
       </c>
       <c r="N20">
-        <v>0.5142626573557766</v>
+        <v>0.4694202807533206</v>
       </c>
       <c r="O20">
-        <v>0.5095296781421683</v>
+        <v>0.51941391332903275</v>
       </c>
       <c r="P20">
-        <v>0.5009982939072178</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.51149553953150706</v>
+      </c>
+      <c r="Q20">
+        <v>0.5066515670492453</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>-0.0205698904552352</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C21">
-        <v>-0.03846214656275225</v>
+        <v>-2.1174623460256042E-2</v>
       </c>
       <c r="D21">
-        <v>-0.1529007092681984</v>
+        <v>-3.8506677642957107E-2</v>
       </c>
       <c r="E21">
-        <v>0.01194369549715431</v>
+        <v>-0.1370404822597894</v>
       </c>
       <c r="F21">
-        <v>0.09040084456202027</v>
+        <v>2.9142550496288239E-2</v>
       </c>
       <c r="G21">
-        <v>0.1266269742124849</v>
+        <v>0.11207045341260451</v>
       </c>
       <c r="H21">
-        <v>0.171535502200363</v>
+        <v>0.1415339034862747</v>
       </c>
       <c r="I21">
-        <v>0.210878844775751</v>
+        <v>0.1769481958881558</v>
       </c>
       <c r="J21">
-        <v>0.2961568981693292</v>
-      </c>
-      <c r="K21">
-        <v>0.335228484302531</v>
+        <v>0.22567303564964711</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.29810304139179461</v>
       </c>
       <c r="L21">
-        <v>0.3575726139428385</v>
+        <v>0.33544682788979829</v>
       </c>
       <c r="M21">
-        <v>0.3477014081003212</v>
+        <v>0.358431520517835</v>
       </c>
       <c r="N21">
-        <v>0.3231851855999194</v>
+        <v>0.34640200339408489</v>
       </c>
       <c r="O21">
-        <v>0.311921706096718</v>
+        <v>0.31867495096664972</v>
       </c>
       <c r="P21">
-        <v>0.3240716900144358</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.31136396955093099</v>
+      </c>
+      <c r="Q21">
+        <v>0.31683170444123188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>-0.02165295856754031</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C22">
-        <v>-0.04033466327126745</v>
+        <v>-2.1853971970998819E-2</v>
       </c>
       <c r="D22">
-        <v>-0.146490266628592</v>
+        <v>-4.1524660839614168E-2</v>
       </c>
       <c r="E22">
-        <v>0.02982315398268879</v>
+        <v>-0.14042674129951571</v>
       </c>
       <c r="F22">
-        <v>0.09788069805077736</v>
+        <v>3.2250244775841208E-2</v>
       </c>
       <c r="G22">
-        <v>0.1226125206553352</v>
+        <v>0.1002674167234207</v>
       </c>
       <c r="H22">
-        <v>0.1492975407677374</v>
+        <v>0.12675269611685791</v>
       </c>
       <c r="I22">
-        <v>0.172053346286706</v>
+        <v>0.15585649536508961</v>
       </c>
       <c r="J22">
-        <v>0.2573578131377989</v>
-      </c>
-      <c r="K22">
-        <v>0.2920314298695409</v>
+        <v>0.1810250657068796</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.26067326575409622</v>
       </c>
       <c r="L22">
-        <v>0.306270313911125</v>
+        <v>0.29959170344723662</v>
       </c>
       <c r="M22">
-        <v>0.3100115922725679</v>
+        <v>0.31973247533750698</v>
       </c>
       <c r="N22">
-        <v>0.3012406652471075</v>
+        <v>0.31818215186229809</v>
       </c>
       <c r="O22">
-        <v>0.2983424163234177</v>
+        <v>0.30851287217781859</v>
       </c>
       <c r="P22">
-        <v>0.2942345940888458</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.30929233473357381</v>
+      </c>
+      <c r="Q22">
+        <v>0.30359242665530661</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>-0.01906016357514158</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C23">
-        <v>-0.08776920225960347</v>
+        <v>-2.075998764515289E-2</v>
       </c>
       <c r="D23">
-        <v>0.06389520843593094</v>
+        <v>-9.0065791659010769E-2</v>
       </c>
       <c r="E23">
-        <v>0.1173658326412301</v>
+        <v>5.7964283717133122E-2</v>
       </c>
       <c r="F23">
-        <v>0.2891305837625077</v>
+        <v>0.10708105243739741</v>
       </c>
       <c r="G23">
-        <v>0.3781610403437616</v>
+        <v>0.28236190816712081</v>
       </c>
       <c r="H23">
-        <v>0.4170614355581234</v>
-      </c>
-      <c r="I23">
-        <v>0.4480213723429537</v>
+        <v>0.36993885188782522</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.40812804974572597</v>
       </c>
       <c r="J23">
-        <v>0.4726251136447324</v>
+        <v>0.44002175237835323</v>
       </c>
       <c r="K23">
-        <v>0.4743426615402531</v>
+        <v>0.46565103053022178</v>
       </c>
       <c r="L23">
-        <v>0.4713507364483198</v>
+        <v>0.47604944811635519</v>
       </c>
       <c r="M23">
-        <v>0.4464887329187834</v>
+        <v>0.4766983703181959</v>
       </c>
       <c r="N23">
-        <v>0.4352375140923365</v>
+        <v>0.45495381775046112</v>
       </c>
       <c r="O23">
-        <v>0.4192497752670303</v>
+        <v>0.43651517225991382</v>
       </c>
       <c r="P23">
-        <v>0.3925506225832374</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.41884805339375769</v>
+      </c>
+      <c r="Q23">
+        <v>0.39361937346418963</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>-0.06949627022102059</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C24">
-        <v>-0.004338283974481131</v>
+        <v>-3.9445118665311578E-2</v>
       </c>
       <c r="D24">
-        <v>0.01562968123723775</v>
+        <v>-0.13750307392636649</v>
       </c>
       <c r="E24">
-        <v>0.00179868509105211</v>
+        <v>-0.15429810777929881</v>
       </c>
       <c r="F24">
-        <v>-0.04822407335791346</v>
+        <v>-0.12580297072886051</v>
       </c>
       <c r="G24">
-        <v>-0.1221385868053295</v>
+        <v>-0.13219155533749821</v>
       </c>
       <c r="H24">
-        <v>-0.09995139933197521</v>
+        <v>-5.9800571242552537E-2</v>
       </c>
       <c r="I24">
-        <v>-0.1103401384903305</v>
+        <v>-0.12566425862777861</v>
       </c>
       <c r="J24">
-        <v>-0.1901370136632914</v>
+        <v>-3.5122388929873079E-2</v>
       </c>
       <c r="K24">
-        <v>-0.333384950037483</v>
+        <v>0.15942691998486419</v>
       </c>
       <c r="L24">
-        <v>-0.3474115673402116</v>
+        <v>0.22593317665289819</v>
       </c>
       <c r="M24">
-        <v>-0.3805542109803519</v>
+        <v>0.26265842062076178</v>
       </c>
       <c r="N24">
-        <v>-0.4453510678172998</v>
+        <v>0.24062645307844921</v>
       </c>
       <c r="O24">
-        <v>-0.5105336010998784</v>
+        <v>0.17440852219163039</v>
       </c>
       <c r="P24">
-        <v>-0.5911555890520964</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.1236621607726464</v>
+      </c>
+      <c r="Q24">
+        <v>5.7889422342563217E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>-0.2583430517767426</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C25">
-        <v>-0.1566754938370986</v>
+        <v>-3.9777296594468603E-2</v>
       </c>
       <c r="D25">
-        <v>-0.1076704839349962</v>
+        <v>-0.14668964214482461</v>
       </c>
       <c r="E25">
-        <v>-0.08862161893716981</v>
+        <v>-0.1533578638397971</v>
       </c>
       <c r="F25">
-        <v>-0.1899631945584164</v>
+        <v>-0.1146524771681655</v>
       </c>
       <c r="G25">
-        <v>-0.2384205929221173</v>
+        <v>-0.11040132119996469</v>
       </c>
       <c r="H25">
-        <v>-0.2426131543421367</v>
+        <v>-9.4466973290522532E-2</v>
       </c>
       <c r="I25">
-        <v>-0.2067698383446986</v>
+        <v>-0.16652272291310249</v>
       </c>
       <c r="J25">
-        <v>-0.2237382482103365</v>
+        <v>-0.1235094222071005</v>
       </c>
       <c r="K25">
-        <v>-0.3106552523148586</v>
+        <v>-3.708598462337484E-2</v>
       </c>
       <c r="L25">
-        <v>-0.3510889005238125</v>
+        <v>0.1791094753449648</v>
       </c>
       <c r="M25">
-        <v>-0.4585189727970073</v>
+        <v>0.21260536822661169</v>
       </c>
       <c r="N25">
-        <v>-0.5564534641182666</v>
+        <v>0.24242481607851149</v>
       </c>
       <c r="O25">
-        <v>-0.6058272786950106</v>
+        <v>0.20534391953058251</v>
       </c>
       <c r="P25">
-        <v>-0.6252563631655124</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1557113190798044</v>
+      </c>
+      <c r="Q25">
+        <v>9.232544023041396E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>-0.0839221464753326</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C26">
-        <v>0.006437852675554847</v>
+        <v>-3.5097712286716702E-2</v>
       </c>
       <c r="D26">
-        <v>0.03983831611714622</v>
+        <v>-0.14879105688454899</v>
       </c>
       <c r="E26">
-        <v>0.07004994796919847</v>
+        <v>-0.12803031401314871</v>
       </c>
       <c r="F26">
-        <v>0.06517887033730711</v>
+        <v>-7.9896874659333081E-2</v>
       </c>
       <c r="G26">
-        <v>0.1038146701557488</v>
+        <v>-0.12227197322723481</v>
       </c>
       <c r="H26">
-        <v>0.1146630030608124</v>
+        <v>-9.0310684316499315E-2</v>
       </c>
       <c r="I26">
-        <v>0.1107674359575307</v>
+        <v>3.6102404273648747E-2</v>
       </c>
       <c r="J26">
-        <v>0.1274161936207352</v>
+        <v>-2.162712005884888E-2</v>
       </c>
       <c r="K26">
-        <v>0.1373979634662869</v>
+        <v>0.12541476290537859</v>
       </c>
       <c r="L26">
-        <v>0.1090555561047262</v>
+        <v>0.22055014877228521</v>
       </c>
       <c r="M26">
-        <v>0.09211447718968319</v>
+        <v>0.22621452131920969</v>
       </c>
       <c r="N26">
-        <v>0.05953964632567278</v>
+        <v>0.1993860266546244</v>
       </c>
       <c r="O26">
-        <v>0.02591590241201679</v>
+        <v>0.1598328053354878</v>
       </c>
       <c r="P26">
-        <v>-0.01310730404467172</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.1091875732390951</v>
+      </c>
+      <c r="Q26">
+        <v>2.9955480566373541E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>-0.1040296974902475</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C27">
-        <v>-0.02500985723389105</v>
+        <v>-4.2397773388044818E-2</v>
       </c>
       <c r="D27">
-        <v>0.07288604337684268</v>
+        <v>-0.15383300861581761</v>
       </c>
       <c r="E27">
-        <v>0.09551600251676144</v>
+        <v>-0.13115286184412711</v>
       </c>
       <c r="F27">
-        <v>0.06361416941514693</v>
+        <v>-8.9353757599278938E-2</v>
       </c>
       <c r="G27">
-        <v>0.06185156010289651</v>
+        <v>-0.1231433059374802</v>
       </c>
       <c r="H27">
-        <v>0.04163502047190994</v>
+        <v>-9.415957885176808E-2</v>
       </c>
       <c r="I27">
-        <v>-0.03076134415629339</v>
+        <v>1.6865610991641911E-2</v>
       </c>
       <c r="J27">
-        <v>-0.01546308073358554</v>
+        <v>-2.553581902148705E-2</v>
       </c>
       <c r="K27">
-        <v>-0.00576167045417045</v>
+        <v>0.1067170811013983</v>
       </c>
       <c r="L27">
-        <v>0.02348242087722173</v>
+        <v>0.26213123495200819</v>
       </c>
       <c r="M27">
-        <v>0.0398647849092462</v>
+        <v>0.29765731605259721</v>
       </c>
       <c r="N27">
-        <v>0.03666277090350639</v>
+        <v>0.30436050077153037</v>
       </c>
       <c r="O27">
-        <v>-0.02824784164257134</v>
+        <v>0.31459199577835639</v>
       </c>
       <c r="P27">
-        <v>-0.07582142370020066</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.29381747684173459</v>
+      </c>
+      <c r="Q27">
+        <v>0.28189050314478081</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>-0.03655537853962401</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C28">
-        <v>-0.1379603409380777</v>
+        <v>-3.784190472112952E-2</v>
       </c>
       <c r="D28">
-        <v>-0.1562057346036211</v>
+        <v>-0.13832858407417589</v>
       </c>
       <c r="E28">
-        <v>-0.1278949530088566</v>
+        <v>-0.1484779268095717</v>
       </c>
       <c r="F28">
-        <v>-0.1315547292904225</v>
+        <v>-0.1105304560027613</v>
       </c>
       <c r="G28">
-        <v>-0.0559316362213273</v>
+        <v>-0.10473490231742801</v>
       </c>
       <c r="H28">
-        <v>-0.124326610391878</v>
+        <v>-8.4908990926140557E-2</v>
       </c>
       <c r="I28">
-        <v>-0.03847781655264771</v>
+        <v>-0.13677070765079161</v>
       </c>
       <c r="J28">
-        <v>0.12914463467778</v>
+        <v>-0.1117303173615906</v>
       </c>
       <c r="K28">
-        <v>0.2217238603036982</v>
+        <v>-3.349959485105114E-2</v>
       </c>
       <c r="L28">
-        <v>0.2611084142165482</v>
+        <v>0.19547600202477011</v>
       </c>
       <c r="M28">
-        <v>0.2382999989415901</v>
+        <v>0.25339280145519438</v>
       </c>
       <c r="N28">
-        <v>0.1695846182240736</v>
+        <v>0.26572643567535642</v>
       </c>
       <c r="O28">
-        <v>0.1214417563471944</v>
+        <v>0.27036663591825438</v>
       </c>
       <c r="P28">
-        <v>0.04342956860031854</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.24920426205017859</v>
+      </c>
+      <c r="Q28">
+        <v>0.25130323487400208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
       </c>
       <c r="B29">
-        <v>-0.04030139197953295</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C29">
-        <v>-0.1469188028521679</v>
+        <v>-4.0553326876614677E-2</v>
       </c>
       <c r="D29">
-        <v>-0.1554252169855284</v>
+        <v>-0.1479538162195814</v>
       </c>
       <c r="E29">
-        <v>-0.1176849214281242</v>
+        <v>-0.15743990045793591</v>
       </c>
       <c r="F29">
-        <v>-0.1109025696496925</v>
+        <v>-0.12338240862939261</v>
       </c>
       <c r="G29">
-        <v>-0.09050104415533768</v>
+        <v>-0.11226507714031531</v>
       </c>
       <c r="H29">
-        <v>-0.1659582073535472</v>
+        <v>-9.217840080306676E-2</v>
       </c>
       <c r="I29">
-        <v>-0.09690093678556788</v>
+        <v>-0.14017573173242789</v>
       </c>
       <c r="J29">
-        <v>-0.01794449358959583</v>
+        <v>-0.1197166476653018</v>
       </c>
       <c r="K29">
-        <v>0.1879528873481787</v>
+        <v>-4.7758584417506571E-2</v>
       </c>
       <c r="L29">
-        <v>0.2215732239682137</v>
+        <v>0.21084603881324121</v>
       </c>
       <c r="M29">
-        <v>0.2508960849237442</v>
+        <v>0.26673410807023251</v>
       </c>
       <c r="N29">
-        <v>0.2176819837218386</v>
+        <v>0.29311776172071929</v>
       </c>
       <c r="O29">
-        <v>0.1672832672493955</v>
+        <v>0.30076538012438409</v>
       </c>
       <c r="P29">
-        <v>0.1078084544016726</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.2916632986213416</v>
+      </c>
+      <c r="Q29">
+        <v>0.2996887411334816</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>45</v>
       </c>
       <c r="B30">
-        <v>-0.03620090780551077</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C30">
-        <v>-0.1480811705231677</v>
+        <v>-3.831418182318809E-2</v>
       </c>
       <c r="D30">
-        <v>-0.1256568238832053</v>
+        <v>-0.14302718790381119</v>
       </c>
       <c r="E30">
-        <v>-0.08306043128572031</v>
+        <v>-0.15614759837233461</v>
       </c>
       <c r="F30">
-        <v>-0.1285681321725141</v>
+        <v>-0.12049862851248461</v>
       </c>
       <c r="G30">
-        <v>-0.09773952707504145</v>
+        <v>-0.11542928046734501</v>
       </c>
       <c r="H30">
-        <v>0.02726915234701851</v>
+        <v>-9.097631206091919E-2</v>
       </c>
       <c r="I30">
-        <v>-0.02818737956976503</v>
+        <v>-0.15390521041131441</v>
       </c>
       <c r="J30">
-        <v>0.1212290350268405</v>
+        <v>-0.1350466831810582</v>
       </c>
       <c r="K30">
-        <v>0.2120546509401655</v>
+        <v>-6.1618431112419048E-2</v>
       </c>
       <c r="L30">
-        <v>0.2145614667769675</v>
+        <v>0.20021368233568659</v>
       </c>
       <c r="M30">
-        <v>0.1974909027126291</v>
+        <v>0.25418407903060369</v>
       </c>
       <c r="N30">
-        <v>0.1590585085271485</v>
+        <v>0.27866226840155078</v>
       </c>
       <c r="O30">
-        <v>0.1043490735310293</v>
+        <v>0.28782913077550948</v>
       </c>
       <c r="P30">
-        <v>0.02991648711076273</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.28789339018815191</v>
+      </c>
+      <c r="Q30">
+        <v>0.30260014931532342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>-0.03989862643544272</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C31">
-        <v>-0.1518112315653981</v>
+        <v>-4.2422741215078393E-2</v>
       </c>
       <c r="D31">
-        <v>-0.1338957677378812</v>
+        <v>-0.14491231685552011</v>
       </c>
       <c r="E31">
-        <v>-0.0864384325116164</v>
+        <v>-0.1537228337438859</v>
       </c>
       <c r="F31">
-        <v>-0.1192510163779714</v>
+        <v>-0.11785106946828761</v>
       </c>
       <c r="G31">
-        <v>-0.09450949721119646</v>
+        <v>-0.1102408660278711</v>
       </c>
       <c r="H31">
-        <v>0.01682253807270365</v>
+        <v>-8.5539583889990667E-2</v>
       </c>
       <c r="I31">
-        <v>-0.03814067753505404</v>
+        <v>-0.13736251335144309</v>
       </c>
       <c r="J31">
-        <v>0.1003362601835343</v>
+        <v>-0.1193058994781326</v>
       </c>
       <c r="K31">
-        <v>0.2509716518112528</v>
+        <v>-4.7607132409206533E-2</v>
       </c>
       <c r="L31">
-        <v>0.2902737486496172</v>
+        <v>0.19420506203296989</v>
       </c>
       <c r="M31">
-        <v>0.302446066930601</v>
+        <v>0.25542254903204847</v>
       </c>
       <c r="N31">
-        <v>0.3047525315274562</v>
+        <v>0.28022837561489577</v>
       </c>
       <c r="O31">
-        <v>0.2873134990890823</v>
+        <v>0.29944601812110871</v>
       </c>
       <c r="P31">
-        <v>0.2779814584931902</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.29294318178999251</v>
+      </c>
+      <c r="Q31">
+        <v>0.31262369790353478</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>-0.0374511855043921</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C32">
-        <v>-0.1418128447619317</v>
+        <v>-3.9930359939206357E-2</v>
       </c>
       <c r="D32">
-        <v>-0.1539841879134369</v>
+        <v>-0.1465127467827731</v>
       </c>
       <c r="E32">
-        <v>-0.1177833549718022</v>
+        <v>-0.15867130046508671</v>
       </c>
       <c r="F32">
-        <v>-0.1087586218372775</v>
+        <v>-0.1238106440316538</v>
       </c>
       <c r="G32">
-        <v>-0.0911558717422651</v>
+        <v>-0.1138376360943303</v>
       </c>
       <c r="H32">
-        <v>-0.1434248502133228</v>
+        <v>-8.9044001999902242E-2</v>
       </c>
       <c r="I32">
-        <v>-0.1232024595211451</v>
+        <v>-0.15370217589589791</v>
       </c>
       <c r="J32">
-        <v>-0.04646328923029547</v>
+        <v>-0.1046709616488484</v>
       </c>
       <c r="K32">
-        <v>0.1900656885014933</v>
+        <v>-3.2059657977283093E-2</v>
       </c>
       <c r="L32">
-        <v>0.2589848795812969</v>
+        <v>0.1947871721389815</v>
       </c>
       <c r="M32">
-        <v>0.2736471227418768</v>
+        <v>0.25285255574778492</v>
       </c>
       <c r="N32">
-        <v>0.2825759093545233</v>
+        <v>0.2748833047793221</v>
       </c>
       <c r="O32">
-        <v>0.259287924861898</v>
+        <v>0.26755114029377491</v>
       </c>
       <c r="P32">
-        <v>0.2617767774258864</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.23502528348344109</v>
+      </c>
+      <c r="Q32">
+        <v>0.2216042435995759</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>-0.03855100065843783</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C33">
-        <v>-0.1458364203379819</v>
+        <v>-4.1226438291630238E-2</v>
       </c>
       <c r="D33">
-        <v>-0.1554155068385158</v>
+        <v>-0.1516714023690903</v>
       </c>
       <c r="E33">
-        <v>-0.1189435655417459</v>
+        <v>-0.1649546506758251</v>
       </c>
       <c r="F33">
-        <v>-0.1092853732113765</v>
+        <v>-0.12788141077995269</v>
       </c>
       <c r="G33">
-        <v>-0.08835563322375663</v>
+        <v>-0.1153150275457443</v>
       </c>
       <c r="H33">
-        <v>-0.1425126700534693</v>
+        <v>-9.4274230545046689E-2</v>
       </c>
       <c r="I33">
-        <v>-0.1142866097231656</v>
+        <v>-0.1539660306036181</v>
       </c>
       <c r="J33">
-        <v>-0.04190825149312326</v>
+        <v>-0.11487675357554381</v>
       </c>
       <c r="K33">
-        <v>0.2152377964582237</v>
+        <v>-4.3309287835111752E-2</v>
       </c>
       <c r="L33">
-        <v>0.2689821499900757</v>
+        <v>0.20690325765777251</v>
       </c>
       <c r="M33">
-        <v>0.287075640589031</v>
+        <v>0.25706716129850488</v>
       </c>
       <c r="N33">
-        <v>0.297862610154289</v>
+        <v>0.27905128009925079</v>
       </c>
       <c r="O33">
-        <v>0.2915081816260456</v>
+        <v>0.26964248250227141</v>
       </c>
       <c r="P33">
-        <v>0.2970764390346991</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.2451782876971271</v>
+      </c>
+      <c r="Q33">
+        <v>0.22753724503712161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>-0.0389621098644793</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C34">
-        <v>-0.1427932469980006</v>
+        <v>-4.1074718625314442E-2</v>
       </c>
       <c r="D34">
-        <v>-0.1543836123777532</v>
+        <v>-0.14724295200378071</v>
       </c>
       <c r="E34">
-        <v>-0.1195624430288047</v>
+        <v>-0.1603009167988951</v>
       </c>
       <c r="F34">
-        <v>-0.1074766133790956</v>
+        <v>-0.1257114164204283</v>
       </c>
       <c r="G34">
-        <v>-0.08264000811508507</v>
+        <v>-0.11544802432454949</v>
       </c>
       <c r="H34">
-        <v>-0.1382879366478705</v>
+        <v>-8.9146536317300476E-2</v>
       </c>
       <c r="I34">
-        <v>-0.1253101007328185</v>
+        <v>-0.14307748280130311</v>
       </c>
       <c r="J34">
-        <v>-0.0509471239179546</v>
+        <v>-0.1139687374578484</v>
       </c>
       <c r="K34">
-        <v>0.206070214879192</v>
+        <v>-5.1603352150574613E-2</v>
       </c>
       <c r="L34">
-        <v>0.2567120358570066</v>
+        <v>0.1885443579908293</v>
       </c>
       <c r="M34">
-        <v>0.2771981279451426</v>
+        <v>0.2472954703415618</v>
       </c>
       <c r="N34">
-        <v>0.2767301747863536</v>
+        <v>0.27760736982739709</v>
       </c>
       <c r="O34">
-        <v>0.2807382162595561</v>
+        <v>0.27589761357676612</v>
       </c>
       <c r="P34">
-        <v>0.2785786803000883</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.25572119833032941</v>
+      </c>
+      <c r="Q34">
+        <v>0.25001437574410817</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>-0.04101509217535057</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C35">
-        <v>-0.1469620907016318</v>
+        <v>-3.8950254876399068E-2</v>
       </c>
       <c r="D35">
-        <v>-0.16320853637771</v>
+        <v>-0.14619186951923069</v>
       </c>
       <c r="E35">
-        <v>-0.1250263332965265</v>
+        <v>-0.15832109244478121</v>
       </c>
       <c r="F35">
-        <v>-0.1167192117371241</v>
+        <v>-0.12388812181905889</v>
       </c>
       <c r="G35">
-        <v>-0.09607719887167776</v>
+        <v>-0.118058327673457</v>
       </c>
       <c r="H35">
-        <v>-0.1598080929976638</v>
+        <v>-9.3662158009411287E-2</v>
       </c>
       <c r="I35">
-        <v>-0.1468917241049291</v>
+        <v>-0.1425697226495812</v>
       </c>
       <c r="J35">
-        <v>-0.07984708411033492</v>
+        <v>-0.1107170773503912</v>
       </c>
       <c r="K35">
-        <v>0.17663947493598</v>
+        <v>-4.4079106632974499E-2</v>
       </c>
       <c r="L35">
-        <v>0.2338593967521249</v>
+        <v>0.206552472395126</v>
       </c>
       <c r="M35">
-        <v>0.2644692177178044</v>
+        <v>0.26260873769053</v>
       </c>
       <c r="N35">
-        <v>0.2825505104338115</v>
+        <v>0.28981143243686253</v>
       </c>
       <c r="O35">
-        <v>0.2783774408157993</v>
+        <v>0.28956317209979188</v>
       </c>
       <c r="P35">
-        <v>0.2976311848615343</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.27463999330015482</v>
+      </c>
+      <c r="Q35">
+        <v>0.26760676563451169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>-0.0414638806154648</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C36">
-        <v>-0.1506406359388672</v>
+        <v>-4.0888338554719593E-2</v>
       </c>
       <c r="D36">
-        <v>-0.1616094968996717</v>
+        <v>-0.15019906974330749</v>
       </c>
       <c r="E36">
-        <v>-0.123184715667589</v>
+        <v>-0.16442235868016819</v>
       </c>
       <c r="F36">
-        <v>-0.1183373584005359</v>
+        <v>-0.12709331955034059</v>
       </c>
       <c r="G36">
-        <v>-0.0981765182965328</v>
+        <v>-0.1160448961145298</v>
       </c>
       <c r="H36">
-        <v>-0.1542454245552607</v>
+        <v>-8.9163496589467775E-2</v>
       </c>
       <c r="I36">
-        <v>-0.1252287271071075</v>
+        <v>-0.14198023397930781</v>
       </c>
       <c r="J36">
-        <v>-0.04947316339679262</v>
+        <v>-0.1160937129387354</v>
       </c>
       <c r="K36">
-        <v>0.1903607909678932</v>
+        <v>-5.2889113977765821E-2</v>
       </c>
       <c r="L36">
-        <v>0.2556031419340437</v>
+        <v>0.18620915505921221</v>
       </c>
       <c r="M36">
-        <v>0.2817982232741989</v>
+        <v>0.24103757684532201</v>
       </c>
       <c r="N36">
-        <v>0.2700978137471752</v>
+        <v>0.27686260342530028</v>
       </c>
       <c r="O36">
-        <v>0.2396085918653446</v>
+        <v>0.29397230279253911</v>
       </c>
       <c r="P36">
-        <v>0.2236310558276528</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.29091898041305581</v>
+      </c>
+      <c r="Q36">
+        <v>0.30799879370042921</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>-0.03921919772846619</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C37">
-        <v>-0.137480108531141</v>
+        <v>-4.4113674927854563E-2</v>
       </c>
       <c r="D37">
-        <v>-0.1475156027379284</v>
+        <v>-0.175483125865217</v>
       </c>
       <c r="E37">
-        <v>-0.1127772008167578</v>
+        <v>-0.11802818912202449</v>
       </c>
       <c r="F37">
-        <v>-0.1054002581183461</v>
+        <v>-6.9351008383463933E-2</v>
       </c>
       <c r="G37">
-        <v>-0.08072847883149102</v>
+        <v>-8.2934323840841956E-2</v>
       </c>
       <c r="H37">
-        <v>-0.1405496486574055</v>
+        <v>-7.1953488757154085E-2</v>
       </c>
       <c r="I37">
-        <v>-0.113401134929879</v>
+        <v>2.3893056001588989E-2</v>
       </c>
       <c r="J37">
-        <v>-0.03948684780998863</v>
+        <v>3.7510526644607987E-2</v>
       </c>
       <c r="K37">
-        <v>0.1933866813988108</v>
+        <v>4.1388868770309471E-2</v>
       </c>
       <c r="L37">
-        <v>0.2554249321929242</v>
+        <v>6.5777093693206404E-2</v>
       </c>
       <c r="M37">
-        <v>0.2835743438069128</v>
+        <v>5.4300084127794537E-2</v>
       </c>
       <c r="N37">
-        <v>0.2687562925303149</v>
+        <v>1.676680796652711E-2</v>
       </c>
       <c r="O37">
-        <v>0.2426314972002794</v>
+        <v>5.5579052844758309E-2</v>
       </c>
       <c r="P37">
-        <v>0.2276630150441347</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>7.964499935825782E-2</v>
+      </c>
+      <c r="Q37">
+        <v>9.3786713005232128E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>-0.03727552558757564</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C38">
-        <v>-0.1435262450151322</v>
+        <v>-4.1883431641257289E-2</v>
       </c>
       <c r="D38">
-        <v>-0.1508318119824851</v>
+        <v>-0.15445228235198319</v>
       </c>
       <c r="E38">
-        <v>-0.1115593143174443</v>
+        <v>-0.12784625387170359</v>
       </c>
       <c r="F38">
-        <v>-0.105614920281805</v>
+        <v>-4.0565253910211402E-2</v>
       </c>
       <c r="G38">
-        <v>-0.08202826358775867</v>
+        <v>2.8011579037234939E-2</v>
       </c>
       <c r="H38">
-        <v>-0.1257921668587328</v>
+        <v>0.1221403107065583</v>
       </c>
       <c r="I38">
-        <v>-0.1105558676181397</v>
+        <v>0.26156140484610091</v>
       </c>
       <c r="J38">
-        <v>-0.04090440103971053</v>
+        <v>0.24719653218532939</v>
       </c>
       <c r="K38">
-        <v>0.1986783197230448</v>
+        <v>0.20448935939244009</v>
       </c>
       <c r="L38">
-        <v>0.2541774640753492</v>
+        <v>0.1839617255291692</v>
       </c>
       <c r="M38">
-        <v>0.2767007878428994</v>
+        <v>0.1972729978514326</v>
       </c>
       <c r="N38">
-        <v>0.2773606710076459</v>
+        <v>0.20154332563146729</v>
       </c>
       <c r="O38">
-        <v>0.2629365165048381</v>
+        <v>0.23716393375164671</v>
       </c>
       <c r="P38">
-        <v>0.2517336270727608</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.26205071389851903</v>
+      </c>
+      <c r="Q38">
+        <v>0.2671213185713931</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>-0.04128336508082256</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C39">
-        <v>-0.1471700609462354</v>
+        <v>-4.3500613226694879E-2</v>
       </c>
       <c r="D39">
-        <v>-0.1564479439541555</v>
+        <v>-0.15177463102381569</v>
       </c>
       <c r="E39">
-        <v>-0.1202866311097909</v>
+        <v>-0.12023340205068039</v>
       </c>
       <c r="F39">
-        <v>-0.1075374350977399</v>
+        <v>-2.59626656364405E-2</v>
       </c>
       <c r="G39">
-        <v>-0.08773565509539887</v>
+        <v>1.202174813282653E-2</v>
       </c>
       <c r="H39">
-        <v>-0.1543869191957263</v>
+        <v>9.8782147739196469E-2</v>
       </c>
       <c r="I39">
-        <v>-0.1179265276884757</v>
+        <v>0.22914328601230249</v>
       </c>
       <c r="J39">
-        <v>-0.04300467859468477</v>
+        <v>0.23388777809278949</v>
       </c>
       <c r="K39">
-        <v>0.1855910746512651</v>
+        <v>0.2481730872492991</v>
       </c>
       <c r="L39">
-        <v>0.2434047180952124</v>
+        <v>0.2509705945330406</v>
       </c>
       <c r="M39">
-        <v>0.269827517579205</v>
+        <v>0.25454335078558638</v>
       </c>
       <c r="N39">
-        <v>0.2674393984388367</v>
+        <v>0.28759747598024321</v>
       </c>
       <c r="O39">
-        <v>0.2486444965570284</v>
+        <v>0.29235512084607462</v>
       </c>
       <c r="P39">
-        <v>0.2413531395492658</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.2845620359837035</v>
+      </c>
+      <c r="Q39">
+        <v>0.29291609845912681</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>-0.04212224482690578</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C40">
-        <v>-0.1421068930745037</v>
+        <v>-6.2947686544932269E-2</v>
       </c>
       <c r="D40">
-        <v>-0.1509030616635356</v>
+        <v>-8.0590003236113344E-2</v>
       </c>
       <c r="E40">
-        <v>-0.1140250191409309</v>
+        <v>8.9044704630449247E-3</v>
       </c>
       <c r="F40">
-        <v>-0.1060251613437894</v>
+        <v>-2.902724034806773E-2</v>
       </c>
       <c r="G40">
-        <v>-0.08727065022843601</v>
+        <v>8.3371800345987013E-2</v>
       </c>
       <c r="H40">
-        <v>-0.1376698124910503</v>
+        <v>0.1493010931918449</v>
       </c>
       <c r="I40">
-        <v>-0.1195011704327201</v>
+        <v>0.115824183607929</v>
       </c>
       <c r="J40">
-        <v>-0.0498602361834714</v>
+        <v>6.6237636918007894E-2</v>
       </c>
       <c r="K40">
-        <v>0.1932400243766574</v>
+        <v>8.5765026763350488E-2</v>
       </c>
       <c r="L40">
-        <v>0.2459475917095718</v>
+        <v>0.13760204355872591</v>
       </c>
       <c r="M40">
-        <v>0.2721054472782695</v>
+        <v>0.14748476775318539</v>
       </c>
       <c r="N40">
-        <v>0.2888374330416307</v>
+        <v>0.17806124672047419</v>
       </c>
       <c r="O40">
-        <v>0.282578705963172</v>
+        <v>0.1740535842982604</v>
       </c>
       <c r="P40">
-        <v>0.3046605728993425</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1410756782304598</v>
+      </c>
+      <c r="Q40">
+        <v>8.1874842195512582E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>-0.04625197306646768</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C41">
-        <v>-0.1749644627007972</v>
+        <v>-5.7688305220132158E-2</v>
       </c>
       <c r="D41">
-        <v>-0.1159657215022772</v>
+        <v>-0.23164583237433509</v>
       </c>
       <c r="E41">
-        <v>-0.08429124641134955</v>
+        <v>-0.15477045682602419</v>
       </c>
       <c r="F41">
-        <v>-0.1028539411078629</v>
+        <v>-0.20298565679968489</v>
       </c>
       <c r="G41">
-        <v>-0.08057460656627742</v>
+        <v>-0.13063326587725549</v>
       </c>
       <c r="H41">
-        <v>0.01695680006807039</v>
+        <v>-0.12575524064482521</v>
       </c>
       <c r="I41">
-        <v>0.04230504136508662</v>
+        <v>-8.9881194713371013E-2</v>
       </c>
       <c r="J41">
-        <v>0.0413959035115388</v>
+        <v>-1.1358904552366E-2</v>
       </c>
       <c r="K41">
-        <v>0.07563392044366418</v>
+        <v>-5.1685224126954372E-2</v>
       </c>
       <c r="L41">
-        <v>0.06653051531235009</v>
+        <v>-7.9862000623029908E-2</v>
       </c>
       <c r="M41">
-        <v>0.02326725599285852</v>
+        <v>-7.1178431259326297E-2</v>
       </c>
       <c r="N41">
-        <v>0.06421266239844411</v>
+        <v>-0.10133037591420491</v>
       </c>
       <c r="O41">
-        <v>0.09191835640753723</v>
+        <v>-0.15828359397581809</v>
       </c>
       <c r="P41">
-        <v>0.102680594596799</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>-0.15462502713086229</v>
+      </c>
+      <c r="Q41">
+        <v>-0.16325357741323099</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>-0.04596243312360057</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C42">
-        <v>-0.1612410354045998</v>
+        <v>-1.9069287103967009E-2</v>
       </c>
       <c r="D42">
-        <v>-0.1344329785429776</v>
+        <v>-0.10778165519950569</v>
       </c>
       <c r="E42">
-        <v>-0.0335130711165406</v>
+        <v>-0.21488466458987551</v>
       </c>
       <c r="F42">
-        <v>0.03536844894231593</v>
+        <v>1.511624141421453E-2</v>
       </c>
       <c r="G42">
-        <v>0.1311091274996921</v>
+        <v>0.1306858090360575</v>
       </c>
       <c r="H42">
-        <v>0.2571426835624245</v>
+        <v>0.17993259341140319</v>
       </c>
       <c r="I42">
-        <v>0.2463051443400934</v>
+        <v>0.30485572106898279</v>
       </c>
       <c r="J42">
-        <v>0.1994795726531932</v>
+        <v>0.31284989829595722</v>
       </c>
       <c r="K42">
-        <v>0.1762284681830604</v>
+        <v>0.29441603808694689</v>
       </c>
       <c r="L42">
-        <v>0.1784867228662888</v>
+        <v>0.34776030632228289</v>
       </c>
       <c r="M42">
-        <v>0.1926409299885658</v>
+        <v>0.35605216296757869</v>
       </c>
       <c r="N42">
-        <v>0.2297963702942683</v>
+        <v>0.34436683625294201</v>
       </c>
       <c r="O42">
-        <v>0.2583333897506042</v>
+        <v>0.33593094280302832</v>
       </c>
       <c r="P42">
-        <v>0.264481407307693</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.33697768078189361</v>
+      </c>
+      <c r="Q42">
+        <v>0.32344020538308171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>-0.04169357859158482</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C43">
-        <v>-0.1505566193668235</v>
+        <v>-2.8114284332585809E-2</v>
       </c>
       <c r="D43">
-        <v>-0.1130696873612765</v>
+        <v>-0.1048979121825331</v>
       </c>
       <c r="E43">
-        <v>-0.02515424914046004</v>
+        <v>-8.3253286653680397E-2</v>
       </c>
       <c r="F43">
-        <v>0.01301548293774969</v>
+        <v>3.6544672004669002E-2</v>
       </c>
       <c r="G43">
-        <v>0.1037820848584118</v>
+        <v>0.1839319398098265</v>
       </c>
       <c r="H43">
-        <v>0.2271858911307</v>
+        <v>0.21354510291239551</v>
       </c>
       <c r="I43">
-        <v>0.239347971302835</v>
+        <v>0.26831085959738321</v>
       </c>
       <c r="J43">
-        <v>0.2367225765627253</v>
+        <v>0.27569443569344448</v>
       </c>
       <c r="K43">
-        <v>0.2433727949278686</v>
+        <v>0.2409840730559126</v>
       </c>
       <c r="L43">
-        <v>0.2406601396667453</v>
+        <v>0.27050098016592888</v>
       </c>
       <c r="M43">
-        <v>0.2740498581576624</v>
+        <v>0.28011319188975842</v>
       </c>
       <c r="N43">
-        <v>0.285143608792408</v>
+        <v>0.27275574364154909</v>
       </c>
       <c r="O43">
-        <v>0.2854242970635281</v>
+        <v>0.24948657488714179</v>
       </c>
       <c r="P43">
-        <v>0.2959337544908345</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>-0.07583542535670965</v>
-      </c>
-      <c r="C44">
-        <v>-0.09944650486294521</v>
-      </c>
-      <c r="D44">
-        <v>0.001743146087469113</v>
-      </c>
-      <c r="E44">
-        <v>-0.0435870779463847</v>
-      </c>
-      <c r="F44">
-        <v>0.07539836301484924</v>
-      </c>
-      <c r="G44">
-        <v>0.1470714847740439</v>
-      </c>
-      <c r="H44">
-        <v>0.1037977607503765</v>
-      </c>
-      <c r="I44">
-        <v>0.05355942527023202</v>
-      </c>
-      <c r="J44">
-        <v>0.0750627242907522</v>
-      </c>
-      <c r="K44">
-        <v>0.1251382065341975</v>
-      </c>
-      <c r="L44">
-        <v>0.1365677807121645</v>
-      </c>
-      <c r="M44">
-        <v>0.1669129164245302</v>
-      </c>
-      <c r="N44">
-        <v>0.1594435112584522</v>
-      </c>
-      <c r="O44">
-        <v>0.1290582635680644</v>
-      </c>
-      <c r="P44">
-        <v>0.07668652557900787</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>-0.05441066455536687</v>
-      </c>
-      <c r="C45">
-        <v>-0.2287525949217221</v>
-      </c>
-      <c r="D45">
-        <v>-0.1474495371313247</v>
-      </c>
-      <c r="E45">
-        <v>-0.2033871772680559</v>
-      </c>
-      <c r="F45">
-        <v>-0.126866305081519</v>
-      </c>
-      <c r="G45">
-        <v>-0.1237991840678845</v>
-      </c>
-      <c r="H45">
-        <v>-0.07606818451582199</v>
-      </c>
-      <c r="I45">
-        <v>-0.005116520260501784</v>
-      </c>
-      <c r="J45">
-        <v>-0.04354419321032169</v>
-      </c>
-      <c r="K45">
-        <v>-0.07567470564610476</v>
-      </c>
-      <c r="L45">
-        <v>-0.06079747423056899</v>
-      </c>
-      <c r="M45">
-        <v>-0.08604719696958087</v>
-      </c>
-      <c r="N45">
-        <v>-0.1404412517322246</v>
-      </c>
-      <c r="O45">
-        <v>-0.1399937231574614</v>
-      </c>
-      <c r="P45">
-        <v>-0.141500291957582</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>-0.01770140893973659</v>
-      </c>
-      <c r="C46">
-        <v>-0.09528614336493811</v>
-      </c>
-      <c r="D46">
-        <v>-0.210684352537194</v>
-      </c>
-      <c r="E46">
-        <v>0.03511873931610918</v>
-      </c>
-      <c r="F46">
-        <v>0.1445570172035717</v>
-      </c>
-      <c r="G46">
-        <v>0.1816916749156593</v>
-      </c>
-      <c r="H46">
-        <v>0.3105309711557367</v>
-      </c>
-      <c r="I46">
-        <v>0.3134531691990743</v>
-      </c>
-      <c r="J46">
-        <v>0.2960020835183754</v>
-      </c>
-      <c r="K46">
-        <v>0.3442058253641982</v>
-      </c>
-      <c r="L46">
-        <v>0.35201646767259</v>
-      </c>
-      <c r="M46">
-        <v>0.3421132654813051</v>
-      </c>
-      <c r="N46">
-        <v>0.3361414766036234</v>
-      </c>
-      <c r="O46">
-        <v>0.3373238563197498</v>
-      </c>
-      <c r="P46">
-        <v>0.3164625982388747</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>-0.02728578359445202</v>
-      </c>
-      <c r="C47">
-        <v>-0.09824768805077648</v>
-      </c>
-      <c r="D47">
-        <v>-0.07834126284727824</v>
-      </c>
-      <c r="E47">
-        <v>0.04054849817349221</v>
-      </c>
-      <c r="F47">
-        <v>0.1851671824408168</v>
-      </c>
-      <c r="G47">
-        <v>0.2101987838532292</v>
-      </c>
-      <c r="H47">
-        <v>0.2677919762366169</v>
-      </c>
-      <c r="I47">
-        <v>0.279588053059001</v>
-      </c>
-      <c r="J47">
-        <v>0.2492805504150287</v>
-      </c>
-      <c r="K47">
-        <v>0.2699624619436021</v>
-      </c>
-      <c r="L47">
-        <v>0.2838699966840019</v>
-      </c>
-      <c r="M47">
-        <v>0.2771843004671938</v>
-      </c>
-      <c r="N47">
-        <v>0.2457349425050634</v>
-      </c>
-      <c r="O47">
-        <v>0.2197119109064018</v>
-      </c>
-      <c r="P47">
-        <v>0.1922180030125828</v>
+        <v>0.2214473741214405</v>
+      </c>
+      <c r="Q43">
+        <v>0.20263714220101439</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:Q43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>